--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-15 23:54:57</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -3633,12 +3633,66 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-03-15 23:54:57</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
           <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>rosset</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>+41 21 313 43 10</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>+41 21 313 43 13 F. +41 21 313 43 10</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>tel: +41 21 313 43 10</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-03-16 02:45:59</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-03-16 02:45:59</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
     </row>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 05:21:18</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-03-16 05:21:18</t>
+          <t>2026-03-16 07:25:23</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-03-16 07:25:23</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -570,26 +570,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aucune photo il y a 28 jours Zimmermann Immobilier 244 m² • Bureau Avenue Blanc, 1202 Genève Superficie de 244 m² Proche des organisations internationales Cuisine entièrement équipée CHF 7’387 CHF 363 m² / year Zimmermann Immobilier Bureau à louer Avenue Blanc, 1202 Genève Jolie arcade dans le quart</t>
+          <t>il y a 4 mois Naef Immobilier – Location 241 m² • Bureau Rue Des Eaux-Vives 94, 1207 Genève Espace lumineux et personnalisable Immeuble certifié Minergie Emplacement privilégié près du lac CHF 9’288 CHF 462 m² / year Naef Immobilier – Location Bureau à louer Rue Des Eaux-Vives 94, 1207 Genève Eaux-V</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>387</v>
+        <v>288</v>
       </c>
       <c r="D3" t="n">
-        <v>244</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>241</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Eaux-Vives</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aucune photo il y a 28 jours Zimmermann Immobilier 244 m² • Bureau Avenue Blanc, 1202 Genève Superficie de 244 m² Proche des organisations internationales Cuisine entièrement équipée CHF 7’387 CHF 363 m² / year Zimmermann Immobilier Bureau à louer Avenue Blanc, 1202 Genève Jolie arcade dans le quartier de Sécheron 244 m² • Bureau Superficie de 244 m² Proche des organisations internationales Cuisine entièrement équipée CHF 7’387 CHF 363 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 241 m² • Bureau Rue Des Eaux-Vives 94, 1207 Genève Espace lumineux et personnalisable Immeuble certifié Minergie Emplacement privilégié près du lac CHF 9’288 CHF 462 m² / year Naef Immobilier – Location Bureau à louer Rue Des Eaux-Vives 94, 1207 Genève Eaux-Vives : bureaux d'env 241m2 à louer 241 m² • Bureau Espace lumineux et personnalisable Immeuble certifié Minergie Emplacement privilégié près du lac CHF 9’288 CHF 462 m² / year</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -601,22 +605,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/avenue-blanc-1202-geneve-JDXL-OVQ4</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/94-rue-des-eaux-vives-1207-geneve-XEG4-2ZZX</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
     </row>
@@ -628,19 +632,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>il y a 1 mois Naef Immobilier – Location 352 m² • Arcade Rue De Richemont 10, 1202 Genève Emplacement idéal près de la gare Options d'aménagement flexibles Deux niveaux plus sous-sol CHF 12’253 CHF 418 m² / year Naef Immobilier – Location Arcade à louer Rue De Richemont 10, 1202 Genève Grande arcade</t>
+          <t>Aucune photo il y a 28 jours Zimmermann Immobilier 244 m² • Bureau Avenue Blanc, 1202 Genève Superficie de 244 m² Proche des organisations internationales Cuisine entièrement équipée CHF 7’387 CHF 363 m² / year Zimmermann Immobilier Bureau à louer Avenue Blanc, 1202 Genève Jolie arcade dans le quart</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>253</v>
+        <v>387</v>
       </c>
       <c r="D4" t="n">
-        <v>352</v>
+        <v>244</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>il y a 1 mois Naef Immobilier – Location 352 m² • Arcade Rue De Richemont 10, 1202 Genève Emplacement idéal près de la gare Options d'aménagement flexibles Deux niveaux plus sous-sol CHF 12’253 CHF 418 m² / year Naef Immobilier – Location Arcade à louer Rue De Richemont 10, 1202 Genève Grande arcade au cur des Pâquis 352 m² • Arcade Emplacement idéal près de la gare Options d'aménagement flexibles Deux niveaux plus sous-sol CHF 12’253 CHF 418 m² / year</t>
+          <t>Aucune photo il y a 28 jours Zimmermann Immobilier 244 m² • Bureau Avenue Blanc, 1202 Genève Superficie de 244 m² Proche des organisations internationales Cuisine entièrement équipée CHF 7’387 CHF 363 m² / year Zimmermann Immobilier Bureau à louer Avenue Blanc, 1202 Genève Jolie arcade dans le quartier de Sécheron 244 m² • Bureau Superficie de 244 m² Proche des organisations internationales Cuisine entièrement équipée CHF 7’387 CHF 363 m² / year</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -659,7 +663,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/10-rue-de-richemont-1202-geneve-NAG4-74X4</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/avenue-blanc-1202-geneve-JDXL-OVQ4</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -669,7 +673,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -686,19 +690,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>il y a 4 mois NESSELL Real Estate SA 5 pièces • 235 m² • Magasin 1205 Genève Idéal pour le yoga et la danse Lumière naturelle abondante Emplacement privilégié près des commerces CHF 7’470 CHF 381 m² / year NESSELL Real Estate SA Magasin à louer 1205 Genève Arcade spacieuse – idéale pour des activité</t>
+          <t>il y a 1 mois Naef Immobilier – Location 352 m² • Arcade Rue De Richemont 10, 1202 Genève Emplacement idéal près de la gare Options d'aménagement flexibles Deux niveaux plus sous-sol CHF 12’253 CHF 418 m² / year Naef Immobilier – Location Arcade à louer Rue De Richemont 10, 1202 Genève Grande arcade</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>470</v>
+        <v>253</v>
       </c>
       <c r="D5" t="n">
-        <v>235</v>
+        <v>352</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>il y a 4 mois NESSELL Real Estate SA 5 pièces • 235 m² • Magasin 1205 Genève Idéal pour le yoga et la danse Lumière naturelle abondante Emplacement privilégié près des commerces CHF 7’470 CHF 381 m² / year NESSELL Real Estate SA Magasin à louer 1205 Genève Arcade spacieuse – idéale pour des activités sportives ou de bien-être 5 pièces • 235 m² • Magasin Idéal pour le yoga et la danse Lumière naturelle abondante Emplacement privilégié près des commerces CHF 7’470 CHF 381 m² / year</t>
+          <t>il y a 1 mois Naef Immobilier – Location 352 m² • Arcade Rue De Richemont 10, 1202 Genève Emplacement idéal près de la gare Options d'aménagement flexibles Deux niveaux plus sous-sol CHF 12’253 CHF 418 m² / year Naef Immobilier – Location Arcade à louer Rue De Richemont 10, 1202 Genève Grande arcade au cur des Pâquis 352 m² • Arcade Emplacement idéal près de la gare Options d'aménagement flexibles Deux niveaux plus sous-sol CHF 12’253 CHF 418 m² / year</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -717,7 +721,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1205-geneve-4E56-OO2M</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/10-rue-de-richemont-1202-geneve-NAG4-74X4</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -727,7 +731,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -744,30 +748,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 2 mois Classicus Real Estate SA 130 m² • Bureau Rue Eugène- Marziano 23, 1227 Les Acacias Espace de travail calme Salle de réunion collaborative Places de parking extérieures CHF 4’320 CHF 399 m² / year Classicus Real Estate SA Bureau à louer Rue Eugène- Marziano 23, 1227 Les Acacias Bureaux </t>
+          <t>il y a 4 mois NESSELL Real Estate SA 5 pièces • 235 m² • Magasin 1205 Genève Idéal pour le yoga et la danse Lumière naturelle abondante Emplacement privilégié près des commerces CHF 7’470 CHF 381 m² / year NESSELL Real Estate SA Magasin à louer 1205 Genève Arcade spacieuse – idéale pour des activité</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>320</v>
+        <v>470</v>
       </c>
       <c r="D6" t="n">
-        <v>130</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Plainpalais</t>
-        </is>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>il y a 2 mois Classicus Real Estate SA 130 m² • Bureau Rue Eugène- Marziano 23, 1227 Les Acacias Espace de travail calme Salle de réunion collaborative Places de parking extérieures CHF 4’320 CHF 399 m² / year Classicus Real Estate SA Bureau à louer Rue Eugène- Marziano 23, 1227 Les Acacias Bureaux professionnels rationnels au 2ème étage - Genève Plainpalais 130 m² • Bureau Espace de travail calme Salle de réunion collaborative Places de parking extérieures CHF 4’320 CHF 399 m² / year</t>
+          <t>il y a 4 mois NESSELL Real Estate SA 5 pièces • 235 m² • Magasin 1205 Genève Idéal pour le yoga et la danse Lumière naturelle abondante Emplacement privilégié près des commerces CHF 7’470 CHF 381 m² / year NESSELL Real Estate SA Magasin à louer 1205 Genève Arcade spacieuse – idéale pour des activités sportives ou de bien-être 5 pièces • 235 m² • Magasin Idéal pour le yoga et la danse Lumière naturelle abondante Emplacement privilégié près des commerces CHF 7’470 CHF 381 m² / year</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/23-rue-eugene-marziano-1227-les-acacias-MXG4-7NR5</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/1205-geneve-4E56-OO2M</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -806,26 +806,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>il y a 3 mois Naef Immobilier – Location 1 pièce • 120 m² • Arcade Rue Arnold- Winkelried 6, 1201 Genève Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year Naef Immobilier – Location Arcade à louer Rue Arnold- Winkelried</t>
+          <t xml:space="preserve">il y a 2 mois Classicus Real Estate SA 130 m² • Bureau Rue Eugène- Marziano 23, 1227 Les Acacias Espace de travail calme Salle de réunion collaborative Places de parking extérieures CHF 4’320 CHF 399 m² / year Classicus Real Estate SA Bureau à louer Rue Eugène- Marziano 23, 1227 Les Acacias Bureaux </t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>460</v>
+        <v>320</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>130</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Plainpalais</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>il y a 3 mois Naef Immobilier – Location 1 pièce • 120 m² • Arcade Rue Arnold- Winkelried 6, 1201 Genève Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year Naef Immobilier – Location Arcade à louer Rue Arnold- Winkelried 6, 1201 Genève Bergues - Arcade hypercentre 120m2 + 50m2 sous sol 1 pièce • 120 m² • Arcade Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year</t>
+          <t>il y a 2 mois Classicus Real Estate SA 130 m² • Bureau Rue Eugène- Marziano 23, 1227 Les Acacias Espace de travail calme Salle de réunion collaborative Places de parking extérieures CHF 4’320 CHF 399 m² / year Classicus Real Estate SA Bureau à louer Rue Eugène- Marziano 23, 1227 Les Acacias Bureaux professionnels rationnels au 2ème étage - Genève Plainpalais 130 m² • Bureau Espace de travail calme Salle de réunion collaborative Places de parking extérieures CHF 4’320 CHF 399 m² / year</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -837,7 +841,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/6-rue-arnold-winkelried-1201-geneve-4E56-OQNE</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/23-rue-eugene-marziano-1227-les-acacias-MXG4-7NR5</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -847,7 +851,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -864,26 +868,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 1 mois Naef Immobilier – Location 206 m² • Bureau Rue Rousseau 38, 1201 Genève Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year Naef Immobilier – Location Bureau à louer Rue Rousseau 38, 1201 Genève Bureau 206m2 à louer  Genève </t>
+          <t>il y a 3 mois Naef Immobilier – Location 1 pièce • 120 m² • Arcade Rue Arnold- Winkelried 6, 1201 Genève Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year Naef Immobilier – Location Arcade à louer Rue Arnold- Winkelried</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>362</v>
+        <v>460</v>
       </c>
       <c r="D8" t="n">
-        <v>206</v>
+        <v>120</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>il y a 1 mois Naef Immobilier – Location 206 m² • Bureau Rue Rousseau 38, 1201 Genève Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year Naef Immobilier – Location Bureau à louer Rue Rousseau 38, 1201 Genève Bureau 206m2 à louer  Genève Centre, proche de la gare Cornavin 206 m² • Bureau Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year</t>
+          <t>il y a 3 mois Naef Immobilier – Location 1 pièce • 120 m² • Arcade Rue Arnold- Winkelried 6, 1201 Genève Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year Naef Immobilier – Location Arcade à louer Rue Arnold- Winkelried 6, 1201 Genève Bergues - Arcade hypercentre 120m2 + 50m2 sous sol 1 pièce • 120 m² • Arcade Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -895,7 +899,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/38-rue-rousseau-1201-geneve-QN34-7LBG</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/6-rue-arnold-winkelried-1201-geneve-4E56-OQNE</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -905,7 +909,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -922,19 +926,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 656 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - </t>
+          <t xml:space="preserve">il y a 1 mois Naef Immobilier – Location 206 m² • Bureau Rue Rousseau 38, 1201 Genève Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year Naef Immobilier – Location Bureau à louer Rue Rousseau 38, 1201 Genève Bureau 206m2 à louer  Genève </t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>947</v>
+        <v>362</v>
       </c>
       <c r="D9" t="n">
-        <v>656</v>
+        <v>206</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 656 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 656 m2 - Surface high techn et industrielle au Cur de Genève 656 m² • Commercial Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year</t>
+          <t>il y a 1 mois Naef Immobilier – Location 206 m² • Bureau Rue Rousseau 38, 1201 Genève Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year Naef Immobilier – Location Bureau à louer Rue Rousseau 38, 1201 Genève Bureau 206m2 à louer  Genève Centre, proche de la gare Cornavin 206 m² • Bureau Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -953,7 +957,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-95R9-E66W</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/38-rue-rousseau-1201-geneve-QN34-7LBG</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -963,7 +967,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -980,19 +984,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 438 m² • Bureau Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year Naef Immobilier – Location Bureau à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - </t>
+          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 656 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - </t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>688</v>
+        <v>947</v>
       </c>
       <c r="D10" t="n">
-        <v>438</v>
+        <v>656</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 438 m² • Bureau Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year Naef Immobilier – Location Bureau à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 438m2 - Bureaux 438 m² • Bureau Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 656 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 656 m2 - Surface high techn et industrielle au Cur de Genève 656 m² • Commercial Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1011,7 +1015,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-XEG4-2OOX</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-95R9-E66W</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1021,7 +1025,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1038,19 +1042,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 3272 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève</t>
+          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 438 m² • Bureau Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year Naef Immobilier – Location Bureau à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - </t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>865</v>
+        <v>688</v>
       </c>
       <c r="D11" t="n">
-        <v>3272</v>
+        <v>438</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 3272 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 3272 m2 - Locaux Tertiaires et Secondaires au Cur de Genève 3272 m² • Commercial Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 438 m² • Bureau Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year Naef Immobilier – Location Bureau à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 438m2 - Bureaux 438 m² • Bureau Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1069,7 +1073,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-LDX9-PVV2</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-XEG4-2OOX</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1079,7 +1083,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1096,19 +1100,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 258 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de La</t>
+          <t>il y a 4 mois Naef Immobilier – Location 3272 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>222</v>
+        <v>865</v>
       </c>
       <c r="D12" t="n">
-        <v>258</v>
+        <v>3272</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 258 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de Lausanne - Bureaux de 258 m² 258 m² • Bureau Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 3272 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 3272 m2 - Locaux Tertiaires et Secondaires au Cur de Genève 3272 m² • Commercial Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1127,7 +1131,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-ZZ74-D5V3</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-LDX9-PVV2</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1141,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1154,19 +1158,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 316 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 12</t>
+          <t>il y a 4 mois Naef Immobilier – Location 258 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de La</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>522</v>
+        <v>222</v>
       </c>
       <c r="D13" t="n">
-        <v>316</v>
+        <v>258</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 316 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureaux de 316 m² au 3ème étage 316 m² • Bureau Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 258 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de Lausanne - Bureaux de 258 m² 258 m² • Bureau Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1185,7 +1189,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-VBG4-7QXW</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-ZZ74-D5V3</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1195,7 +1199,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1212,19 +1216,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 266 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantep</t>
+          <t>il y a 4 mois Naef Immobilier – Location 316 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 12</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>637</v>
+        <v>522</v>
       </c>
       <c r="D14" t="n">
-        <v>266</v>
+        <v>316</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 266 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureau de 266m² aux derniers étages 266 m² • Bureau Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 316 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureaux de 316 m² au 3ème étage 316 m² • Bureau Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1243,7 +1247,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-23ZJ-WQ7B</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-VBG4-7QXW</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1253,7 +1257,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1270,26 +1274,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 162 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève C</t>
+          <t>il y a 4 mois Naef Immobilier – Location 266 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantep</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>276</v>
+        <v>637</v>
       </c>
       <c r="D15" t="n">
-        <v>162</v>
+        <v>266</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 162 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureau au 1er étage de 162 m² quartier dynamique 162 m² • Bureau Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 266 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureau de 266m² aux derniers étages 266 m² • Bureau Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1301,7 +1305,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-LDX9-PZPW</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-23ZJ-WQ7B</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1311,7 +1315,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1328,24 +1332,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade </t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>il y a 4 mois Naef Immobilier – Location 162 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève C</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>276</v>
+      </c>
       <c r="D16" t="n">
-        <v>260</v>
+        <v>162</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 260m2 à louer  Quartier des Charmilles, Genève 260 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 162 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureau au 1er étage de 162 m² quartier dynamique 162 m² • Bureau Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1357,7 +1363,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-95R9-G6P5</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-LDX9-PZPW</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1367,7 +1373,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1384,28 +1390,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système </t>
+          <t xml:space="preserve">il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade </t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>164</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Rive</t>
-        </is>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande</t>
+          <t>il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 260m2 à louer  Quartier des Charmilles, Genève 260 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1417,7 +1419,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/11-cours-de-rive-1204-geneve-VBG4-7VZQ</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-95R9-G6P5</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1427,7 +1429,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1444,24 +1446,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade c</t>
+          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système </t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>130</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
+        <v>164</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Rive</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 130m2 à louer  Quartier des Charmilles, Genève 130 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1473,7 +1479,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-XEG4-9ONV</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/11-cours-de-rive-1204-geneve-VBG4-7VZQ</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1483,7 +1489,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1500,24 +1506,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • </t>
+          <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade c</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>770</v>
+        <v>130</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • Bureau Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year</t>
+          <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 130m2 à louer  Quartier des Charmilles, Genève 130 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1529,7 +1535,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/rue-jean-jaquet-1201-geneve-WRG4-9WBO</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-XEG4-9ONV</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1539,7 +1545,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1556,17 +1562,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Sur</t>
+          <t xml:space="preserve">il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • </t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>1351</v>
+        <v>770</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Surface de 1'351 m² sur deux niveaux 1351 m² • Bureau Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande</t>
+          <t>il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • Bureau Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1585,7 +1591,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/7-rue-barton-1201-geneve-MXG4-NW29</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/rue-jean-jaquet-1201-geneve-WRG4-9WBO</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1595,7 +1601,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1612,17 +1618,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genèv</t>
+          <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Sur</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>205</v>
+        <v>1351</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de Lausanne - Bureaux d'env. 205 m² 205 m² • Bureau Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Surface de 1'351 m² sur deux niveaux 1351 m² • Bureau Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1641,7 +1647,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-WRG4-DVXX</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/7-rue-barton-1201-geneve-MXG4-NW29</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1651,7 +1657,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1668,26 +1674,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 28 jours Zimmermann Immobilier 2 pièces • 22 m² • Bureau Place De Cornavin, 1201 Genève Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year Zimmermann Immobilier Bureau à louer Place De Cornavin, 1201 Genève Bureau privatif </t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>550</v>
-      </c>
+          <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genèv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>il y a 28 jours Zimmermann Immobilier 2 pièces • 22 m² • Bureau Place De Cornavin, 1201 Genève Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year Zimmermann Immobilier Bureau à louer Place De Cornavin, 1201 Genève Bureau privatif de 14 m² dans grand espace partagé- 14 m² - en face de la Gare Cornavin 2 pièces • 22 m² • Bureau Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de Lausanne - Bureaux d'env. 205 m² 205 m² • Bureau Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1699,7 +1703,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/place-de-cornavin-1201-geneve-VBG4-9ZEO</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-WRG4-DVXX</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1709,7 +1713,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1726,26 +1730,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>il y a 1 mois Naef Immobilier – Location Bureau Rue Des Deux-Ponts 27, 1205 Genève Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178 - Naef Immobilier – Location Bureau à louer Rue Des Deux-Ponts 27, 1205 Genève Emplacement publicitaire pour une enseigne - Genève Pla</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Plainpalais</t>
-        </is>
-      </c>
+          <t xml:space="preserve">il y a 28 jours Zimmermann Immobilier 2 pièces • 22 m² • Bureau Place De Cornavin, 1201 Genève Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year Zimmermann Immobilier Bureau à louer Place De Cornavin, 1201 Genève Bureau privatif </t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>550</v>
+      </c>
+      <c r="D23" t="n">
+        <v>22</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>il y a 1 mois Naef Immobilier – Location Bureau Rue Des Deux-Ponts 27, 1205 Genève Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178 - Naef Immobilier – Location Bureau à louer Rue Des Deux-Ponts 27, 1205 Genève Emplacement publicitaire pour une enseigne - Genève Plainpalais Bureau Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178</t>
+          <t>il y a 28 jours Zimmermann Immobilier 2 pièces • 22 m² • Bureau Place De Cornavin, 1201 Genève Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year Zimmermann Immobilier Bureau à louer Place De Cornavin, 1201 Genève Bureau privatif de 14 m² dans grand espace partagé- 14 m² - en face de la Gare Cornavin 2 pièces • 22 m² • Bureau Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1757,7 +1761,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/27-rue-des-deux-ponts-1205-geneve-23ZJ-9XPW</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/place-de-cornavin-1201-geneve-VBG4-9ZEO</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1767,7 +1771,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1784,19 +1788,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>il y a 2 mois NSR-Group S.A Garage Chemin de Roches, 1207 Genève Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400 - NSR-Group S.A Garage à louer Chemin de Roches, 1207 Genève Eaux-Vives - Box zu vermieten Garage Emplacement facilement accessible Portail de</t>
+          <t>il y a 1 mois Naef Immobilier – Location Bureau Rue Des Deux-Ponts 27, 1205 Genève Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178 - Naef Immobilier – Location Bureau à louer Rue Des Deux-Ponts 27, 1205 Genève Emplacement publicitaire pour une enseigne - Genève Pla</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eaux-Vives</t>
+          <t>Plainpalais</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>il y a 2 mois NSR-Group S.A Garage Chemin de Roches, 1207 Genève Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400 - NSR-Group S.A Garage à louer Chemin de Roches, 1207 Genève Eaux-Vives - Box zu vermieten Garage Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400</t>
+          <t>il y a 1 mois Naef Immobilier – Location Bureau Rue Des Deux-Ponts 27, 1205 Genève Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178 - Naef Immobilier – Location Bureau à louer Rue Des Deux-Ponts 27, 1205 Genève Emplacement publicitaire pour une enseigne - Genève Plainpalais Bureau Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1815,7 +1819,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/chemin-de-roches-1207-geneve-8VBP-BWZW</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/27-rue-des-deux-ponts-1205-geneve-23ZJ-9XPW</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1825,7 +1829,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1883,7 +1887,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1941,7 +1945,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1999,7 +2003,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2016,36 +2020,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
+          <t>il y a 2 mois NSR-Group S.A Garage Chemin de Roches, 1207 Genève Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400 - NSR-Group S.A Garage à louer Chemin de Roches, 1207 Genève Eaux-Vives - Box zu vermieten Garage Emplacement facilement accessible Portail de</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
-        <v>35</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Eaux-Vives</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
+          <t>il y a 2 mois NSR-Group S.A Garage Chemin de Roches, 1207 Genève Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400 - NSR-Group S.A Garage à louer Chemin de Roches, 1207 Genève Eaux-Vives - Box zu vermieten Garage Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-Y235-5V7W</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/chemin-de-roches-1207-geneve-8VBP-BWZW</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2060,7 +2066,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
     </row>
@@ -2072,22 +2078,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Local commercial</t>
+          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>35</v>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Local commercial</t>
+          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2099,7 +2107,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-Y235-5V7W</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2109,7 +2117,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2126,7 +2134,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Canton de Genève</t>
+          <t>Local commercial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -2134,7 +2142,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Canton de Genève</t>
+          <t>Local commercial</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2153,7 +2161,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/canton-geneve/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2163,7 +2171,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2180,7 +2188,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer</t>
+          <t>Canton de Genève</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -2188,7 +2196,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer</t>
+          <t>Canton de Genève</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2207,7 +2215,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-geneve/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/canton-geneve/commercial</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2217,7 +2225,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2234,7 +2242,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
+          <t>Locaux commerciaux à louer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -2242,7 +2250,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
+          <t>Locaux commerciaux à louer</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2261,7 +2269,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-bouchet-moillebeau/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-geneve/commercial</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2271,7 +2279,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2288,7 +2296,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
+          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -2296,7 +2304,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
+          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2315,7 +2323,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-cluse-philosophes/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-bouchet-moillebeau/commercial</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2325,7 +2333,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2342,7 +2350,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
+          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -2350,7 +2358,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
+          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2369,7 +2377,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-grand-pre-vermont/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-cluse-philosophes/commercial</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2379,7 +2387,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2396,7 +2404,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
+          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -2404,7 +2412,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
+          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2423,7 +2431,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-st-gervais-chantepoulet/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-grand-pre-vermont/commercial</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2433,7 +2441,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2450,7 +2458,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
+          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -2458,7 +2466,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
+          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2477,7 +2485,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-paquis-navigation/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-st-gervais-chantepoulet/commercial</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2487,7 +2495,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2504,7 +2512,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à ONU - Rigot</t>
+          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -2512,7 +2520,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à ONU - Rigot</t>
+          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2531,7 +2539,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-onu-rigot/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-paquis-navigation/commercial</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2541,7 +2549,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2558,7 +2566,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
+          <t>Locaux commerciaux à louer à ONU - Rigot</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -2566,7 +2574,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
+          <t>Locaux commerciaux à louer à ONU - Rigot</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2585,7 +2593,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-secheron-prieure/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-onu-rigot/commercial</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2595,7 +2603,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2612,7 +2620,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cité - Centre</t>
+          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -2620,7 +2628,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cité - Centre</t>
+          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2639,7 +2647,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-cite-centre/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-secheron-prieure/commercial</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2649,7 +2657,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2666,7 +2674,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
+          <t>Locaux commerciaux à louer à Cité - Centre</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2674,7 +2682,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
+          <t>Locaux commerciaux à louer à Cité - Centre</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2693,7 +2701,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-charmilles-chatelaine/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-cite-centre/commercial</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2703,7 +2711,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2720,7 +2728,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
+          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2728,7 +2736,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
+          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2747,7 +2755,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-st-jean-aire/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-charmilles-chatelaine/commercial</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2757,7 +2765,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2774,7 +2782,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
+          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -2782,7 +2790,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
+          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2801,7 +2809,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-florissant-malagnou/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-st-jean-aire/commercial</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2811,7 +2819,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2828,19 +2836,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
+          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Acacias</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
+          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2859,7 +2863,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-batie-acacias/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-florissant-malagnou/commercial</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2869,7 +2873,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -2886,15 +2890,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Délices - Grottes</t>
+          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Acacias</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Délices - Grottes</t>
+          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2913,7 +2921,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-delices-grottes/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-batie-acacias/commercial</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2923,7 +2931,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -2940,19 +2948,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
+          <t>Locaux commerciaux à louer à Délices - Grottes</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Acacias</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
+          <t>Locaux commerciaux à louer à Délices - Grottes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2971,7 +2975,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1227-les-acacias/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-delices-grottes/commercial</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2981,7 +2985,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -2998,15 +3002,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Vernier</t>
+          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Acacias</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Vernier</t>
+          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3025,7 +3033,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-vernier/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1227-les-acacias/commercial</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3035,7 +3043,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3052,7 +3060,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Lancy</t>
+          <t>Locaux commerciaux à louer à Vernier</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -3060,7 +3068,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Lancy</t>
+          <t>Locaux commerciaux à louer à Vernier</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3079,7 +3087,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-lancy/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-vernier/commercial</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3089,7 +3097,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3106,7 +3114,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Meyrin</t>
+          <t>Locaux commerciaux à louer à Lancy</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -3114,7 +3122,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Meyrin</t>
+          <t>Locaux commerciaux à louer à Lancy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3133,7 +3141,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-meyrin/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-lancy/commercial</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3143,7 +3151,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3160,19 +3168,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
+          <t>Locaux commerciaux à louer à Meyrin</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Carouge</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
+          <t>Locaux commerciaux à louer à Meyrin</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3191,7 +3195,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1227-carouge-ge/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-meyrin/commercial</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3201,7 +3205,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3218,15 +3222,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Onex (1213)</t>
+          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Carouge</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Onex (1213)</t>
+          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3245,7 +3253,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1213-onex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1227-carouge-ge/commercial</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3255,7 +3263,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3272,7 +3280,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Thônex (1226)</t>
+          <t>Locaux commerciaux à louer à Onex (1213)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -3280,7 +3288,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Thônex (1226)</t>
+          <t>Locaux commerciaux à louer à Onex (1213)</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3299,7 +3307,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1226-thonex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1213-onex/commercial</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3309,7 +3317,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3326,7 +3334,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
+          <t>Locaux commerciaux à louer à Thônex (1226)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -3334,7 +3342,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
+          <t>Locaux commerciaux à louer à Thônex (1226)</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3353,7 +3361,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-le-grand-saconnex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1226-thonex/commercial</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3363,7 +3371,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3380,7 +3388,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
+          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -3388,7 +3396,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
+          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3407,7 +3415,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-chene-bougeries/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-le-grand-saconnex/commercial</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3417,7 +3425,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3434,7 +3442,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Veyrier</t>
+          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -3442,7 +3450,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Veyrier</t>
+          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3461,7 +3469,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-veyrier/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-chene-bougeries/commercial</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3471,7 +3479,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3488,7 +3496,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
+          <t>Locaux commerciaux à louer à Veyrier</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -3496,7 +3504,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
+          <t>Locaux commerciaux à louer à Veyrier</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3515,7 +3523,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1228-plan-les-ouates/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-veyrier/commercial</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3525,7 +3533,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -3542,7 +3550,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -3550,7 +3558,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3569,7 +3577,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1233-bernex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1228-plan-les-ouates/commercial</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3579,7 +3587,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -3596,7 +3604,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+          <t>Locaux commerciaux à louer à Bernex (1233)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -3604,7 +3612,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+          <t>Locaux commerciaux à louer à Bernex (1233)</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3623,7 +3631,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1225-chene-bourg/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1233-bernex/commercial</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3633,7 +3641,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -3645,12 +3653,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>rosset</t>
+          <t>realadvisor</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>+41 21 313 43 10</t>
+          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -3658,39 +3666,93 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
+          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1225-chene-bourg/commercial</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-03-16 13:22:39</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>rosset</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>+41 21 313 43 10</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>+41 21 313 43 13 F. +41 21 313 43 10</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>tel: +41 21 313 43 10</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>2026-03-16 02:45:59</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2026-03-16 10:10:13</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-03-16 13:22:39</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>2026-03-16 02:45:59</t>
         </is>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
+          <t>il y a 3 jours Segimo SA Bureau 1203 Genève 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000 - Segimo SA Bureau à louer 1203 Genève Coworking professionnel pour architecte dans les locaux d'un promoteur immobilier à 1203 Genève Bureau 35 m² entièrement rénovés Cui</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -2088,7 +2088,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
+          <t>il y a 3 jours Segimo SA Bureau 1203 Genève 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000 - Segimo SA Bureau à louer 1203 Genève Coworking professionnel pour architecte dans les locaux d'un promoteur immobilier à 1203 Genève Bureau 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2107,22 +2107,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-Y235-5V7W</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-KQNL-GWW5</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
     </row>
@@ -2134,34 +2134,36 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Local commercial</t>
+          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>35</v>
+      </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Local commercial</t>
+          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-Y235-5V7W</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2176,7 +2178,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2190,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Canton de Genève</t>
+          <t>Local commercial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -2196,7 +2198,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Canton de Genève</t>
+          <t>Local commercial</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2215,7 +2217,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/canton-geneve/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2225,7 +2227,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2242,7 +2244,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer</t>
+          <t>Canton de Genève</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -2250,7 +2252,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer</t>
+          <t>Canton de Genève</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2269,7 +2271,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-geneve/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/canton-geneve/commercial</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2279,7 +2281,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2296,7 +2298,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
+          <t>Locaux commerciaux à louer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -2304,7 +2306,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
+          <t>Locaux commerciaux à louer</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2323,7 +2325,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-bouchet-moillebeau/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-geneve/commercial</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2333,7 +2335,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2350,7 +2352,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
+          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -2358,7 +2360,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
+          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2377,7 +2379,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-cluse-philosophes/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-bouchet-moillebeau/commercial</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2387,7 +2389,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2404,7 +2406,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
+          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -2412,7 +2414,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
+          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2431,7 +2433,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-grand-pre-vermont/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-cluse-philosophes/commercial</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2441,7 +2443,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2458,7 +2460,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
+          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -2466,7 +2468,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
+          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2485,7 +2487,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-st-gervais-chantepoulet/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-grand-pre-vermont/commercial</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2495,7 +2497,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2512,7 +2514,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
+          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -2520,7 +2522,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
+          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2539,7 +2541,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-paquis-navigation/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-st-gervais-chantepoulet/commercial</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2549,7 +2551,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2566,7 +2568,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à ONU - Rigot</t>
+          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -2574,7 +2576,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à ONU - Rigot</t>
+          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2593,7 +2595,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-onu-rigot/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-paquis-navigation/commercial</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2603,7 +2605,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2620,7 +2622,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
+          <t>Locaux commerciaux à louer à ONU - Rigot</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -2628,7 +2630,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
+          <t>Locaux commerciaux à louer à ONU - Rigot</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2647,7 +2649,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-secheron-prieure/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-onu-rigot/commercial</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2657,7 +2659,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2674,7 +2676,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cité - Centre</t>
+          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2682,7 +2684,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cité - Centre</t>
+          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2701,7 +2703,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-cite-centre/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-secheron-prieure/commercial</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2711,7 +2713,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2728,7 +2730,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
+          <t>Locaux commerciaux à louer à Cité - Centre</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2736,7 +2738,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
+          <t>Locaux commerciaux à louer à Cité - Centre</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2755,7 +2757,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-charmilles-chatelaine/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-cite-centre/commercial</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2765,7 +2767,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2782,7 +2784,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
+          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -2790,7 +2792,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
+          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2809,7 +2811,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-st-jean-aire/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-charmilles-chatelaine/commercial</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2819,7 +2821,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2836,7 +2838,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
+          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -2844,7 +2846,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
+          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2863,7 +2865,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-florissant-malagnou/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-st-jean-aire/commercial</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2873,7 +2875,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -2890,19 +2892,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
+          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Acacias</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
+          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2921,7 +2919,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-batie-acacias/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-florissant-malagnou/commercial</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2931,7 +2929,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -2948,15 +2946,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Délices - Grottes</t>
+          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Acacias</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Délices - Grottes</t>
+          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2975,7 +2977,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-delices-grottes/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-batie-acacias/commercial</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2985,7 +2987,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3002,19 +3004,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
+          <t>Locaux commerciaux à louer à Délices - Grottes</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Acacias</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
+          <t>Locaux commerciaux à louer à Délices - Grottes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3033,7 +3031,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1227-les-acacias/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-delices-grottes/commercial</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3043,7 +3041,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3060,15 +3058,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Vernier</t>
+          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Acacias</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Vernier</t>
+          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3087,7 +3089,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-vernier/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1227-les-acacias/commercial</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3097,7 +3099,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3114,7 +3116,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Lancy</t>
+          <t>Locaux commerciaux à louer à Vernier</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -3122,7 +3124,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Lancy</t>
+          <t>Locaux commerciaux à louer à Vernier</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3141,7 +3143,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-lancy/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-vernier/commercial</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3151,7 +3153,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3168,7 +3170,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Meyrin</t>
+          <t>Locaux commerciaux à louer à Lancy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -3176,7 +3178,7 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Meyrin</t>
+          <t>Locaux commerciaux à louer à Lancy</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3195,7 +3197,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-meyrin/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-lancy/commercial</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3205,7 +3207,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3222,19 +3224,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
+          <t>Locaux commerciaux à louer à Meyrin</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Carouge</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
+          <t>Locaux commerciaux à louer à Meyrin</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3253,7 +3251,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1227-carouge-ge/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-meyrin/commercial</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3263,7 +3261,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3280,15 +3278,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Onex (1213)</t>
+          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Carouge</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Onex (1213)</t>
+          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3307,7 +3309,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1213-onex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1227-carouge-ge/commercial</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3317,7 +3319,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3334,7 +3336,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Thônex (1226)</t>
+          <t>Locaux commerciaux à louer à Onex (1213)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -3342,7 +3344,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Thônex (1226)</t>
+          <t>Locaux commerciaux à louer à Onex (1213)</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3361,7 +3363,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1226-thonex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1213-onex/commercial</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3371,7 +3373,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3388,7 +3390,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
+          <t>Locaux commerciaux à louer à Thônex (1226)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -3396,7 +3398,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
+          <t>Locaux commerciaux à louer à Thônex (1226)</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3415,7 +3417,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-le-grand-saconnex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1226-thonex/commercial</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3425,7 +3427,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3442,7 +3444,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
+          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -3450,7 +3452,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
+          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3469,7 +3471,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-chene-bougeries/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-le-grand-saconnex/commercial</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3479,7 +3481,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3496,7 +3498,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Veyrier</t>
+          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -3504,7 +3506,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Veyrier</t>
+          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3523,7 +3525,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-veyrier/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-chene-bougeries/commercial</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3533,7 +3535,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -3550,7 +3552,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
+          <t>Locaux commerciaux à louer à Veyrier</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -3558,7 +3560,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
+          <t>Locaux commerciaux à louer à Veyrier</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3577,7 +3579,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1228-plan-les-ouates/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-veyrier/commercial</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3587,7 +3589,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -3604,7 +3606,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -3612,7 +3614,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3631,7 +3633,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1233-bernex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1228-plan-les-ouates/commercial</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3641,7 +3643,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -3658,7 +3660,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+          <t>Locaux commerciaux à louer à Bernex (1233)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -3666,7 +3668,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+          <t>Locaux commerciaux à louer à Bernex (1233)</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3685,7 +3687,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1225-chene-bourg/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1233-bernex/commercial</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3695,7 +3697,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -3707,12 +3709,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>rosset</t>
+          <t>realadvisor</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>+41 21 313 43 10</t>
+          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3720,39 +3722,93 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
+          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1225-chene-bourg/commercial</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:10:21</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>rosset</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>+41 21 313 43 10</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>+41 21 313 43 13 F. +41 21 313 43 10</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>tel: +41 21 313 43 10</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>2026-03-16 02:45:59</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>2026-03-16 13:22:39</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:10:21</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>2026-03-16 02:45:59</t>
         </is>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
+          <t>il y a 4 heures Segimo SA 35 m² • Bureau 1203 Genève Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande - Segimo SA Bureau à louer 1203 Genève 35 m² • Bureau Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -2144,7 +2144,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
+          <t>il y a 4 heures Segimo SA 35 m² • Bureau 1203 Genève Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande - Segimo SA Bureau à louer 1203 Genève 35 m² • Bureau Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2158,27 +2158,27 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-Y235-5V7W</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-8OOA-XD6Z</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
     </row>
@@ -2190,34 +2190,36 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Local commercial</t>
+          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>35</v>
+      </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Local commercial</t>
+          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-Y235-5V7W</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2227,12 +2229,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>2026-03-16 13:22:39</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>2026-03-16 16:10:21</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2246,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Canton de Genève</t>
+          <t>Local commercial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -2252,7 +2254,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Canton de Genève</t>
+          <t>Local commercial</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2271,7 +2273,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/canton-geneve/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2281,7 +2283,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2298,7 +2300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer</t>
+          <t>Canton de Genève</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -2306,7 +2308,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer</t>
+          <t>Canton de Genève</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2325,7 +2327,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-geneve/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/canton-geneve/commercial</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2335,7 +2337,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2352,7 +2354,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
+          <t>Locaux commerciaux à louer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -2360,7 +2362,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
+          <t>Locaux commerciaux à louer</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2379,7 +2381,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-bouchet-moillebeau/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-geneve/commercial</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2389,7 +2391,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2406,7 +2408,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
+          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -2414,7 +2416,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
+          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2433,7 +2435,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-cluse-philosophes/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-bouchet-moillebeau/commercial</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2443,7 +2445,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2460,7 +2462,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
+          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -2468,7 +2470,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
+          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2487,7 +2489,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-grand-pre-vermont/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-cluse-philosophes/commercial</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2497,7 +2499,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2514,7 +2516,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
+          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -2522,7 +2524,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
+          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2541,7 +2543,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-st-gervais-chantepoulet/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-grand-pre-vermont/commercial</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2551,7 +2553,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2568,7 +2570,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
+          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -2576,7 +2578,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
+          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2595,7 +2597,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-paquis-navigation/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-st-gervais-chantepoulet/commercial</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2605,7 +2607,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2622,7 +2624,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à ONU - Rigot</t>
+          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -2630,7 +2632,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à ONU - Rigot</t>
+          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2649,7 +2651,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-onu-rigot/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-paquis-navigation/commercial</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2659,7 +2661,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2676,7 +2678,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
+          <t>Locaux commerciaux à louer à ONU - Rigot</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2684,7 +2686,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
+          <t>Locaux commerciaux à louer à ONU - Rigot</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2703,7 +2705,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-secheron-prieure/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-onu-rigot/commercial</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2713,7 +2715,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2730,7 +2732,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cité - Centre</t>
+          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2738,7 +2740,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cité - Centre</t>
+          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2757,7 +2759,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-cite-centre/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-secheron-prieure/commercial</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2767,7 +2769,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2784,7 +2786,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
+          <t>Locaux commerciaux à louer à Cité - Centre</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -2792,7 +2794,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
+          <t>Locaux commerciaux à louer à Cité - Centre</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2811,7 +2813,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-charmilles-chatelaine/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-cite-centre/commercial</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2821,7 +2823,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2838,7 +2840,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
+          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -2846,7 +2848,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
+          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2865,7 +2867,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-st-jean-aire/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-charmilles-chatelaine/commercial</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2875,7 +2877,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -2892,7 +2894,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
+          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -2900,7 +2902,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
+          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2919,7 +2921,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-florissant-malagnou/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-st-jean-aire/commercial</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2929,7 +2931,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -2946,19 +2948,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
+          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Acacias</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
+          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2977,7 +2975,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-batie-acacias/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-florissant-malagnou/commercial</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2987,7 +2985,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3004,15 +3002,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Délices - Grottes</t>
+          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Acacias</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Délices - Grottes</t>
+          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3031,7 +3033,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-delices-grottes/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-batie-acacias/commercial</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3041,7 +3043,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3058,19 +3060,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
+          <t>Locaux commerciaux à louer à Délices - Grottes</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Acacias</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
+          <t>Locaux commerciaux à louer à Délices - Grottes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3089,7 +3087,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1227-les-acacias/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-delices-grottes/commercial</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3099,7 +3097,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3116,15 +3114,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Vernier</t>
+          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Acacias</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Vernier</t>
+          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3143,7 +3145,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-vernier/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1227-les-acacias/commercial</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3153,7 +3155,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3170,7 +3172,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Lancy</t>
+          <t>Locaux commerciaux à louer à Vernier</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -3178,7 +3180,7 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Lancy</t>
+          <t>Locaux commerciaux à louer à Vernier</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3197,7 +3199,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-lancy/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-vernier/commercial</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3207,7 +3209,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3224,7 +3226,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Meyrin</t>
+          <t>Locaux commerciaux à louer à Lancy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -3232,7 +3234,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Meyrin</t>
+          <t>Locaux commerciaux à louer à Lancy</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3251,7 +3253,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-meyrin/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-lancy/commercial</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3261,7 +3263,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3278,19 +3280,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
+          <t>Locaux commerciaux à louer à Meyrin</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Carouge</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
+          <t>Locaux commerciaux à louer à Meyrin</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3309,7 +3307,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1227-carouge-ge/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-meyrin/commercial</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3319,7 +3317,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3336,15 +3334,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Onex (1213)</t>
+          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Carouge</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Onex (1213)</t>
+          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3363,7 +3365,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1213-onex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1227-carouge-ge/commercial</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3373,7 +3375,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3390,7 +3392,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Thônex (1226)</t>
+          <t>Locaux commerciaux à louer à Onex (1213)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -3398,7 +3400,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Thônex (1226)</t>
+          <t>Locaux commerciaux à louer à Onex (1213)</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3417,7 +3419,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1226-thonex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1213-onex/commercial</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3427,7 +3429,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3444,7 +3446,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
+          <t>Locaux commerciaux à louer à Thônex (1226)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -3452,7 +3454,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
+          <t>Locaux commerciaux à louer à Thônex (1226)</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3471,7 +3473,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-le-grand-saconnex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1226-thonex/commercial</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3481,7 +3483,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3498,7 +3500,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
+          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -3506,7 +3508,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
+          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3525,7 +3527,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-chene-bougeries/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-le-grand-saconnex/commercial</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3535,7 +3537,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -3552,7 +3554,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Veyrier</t>
+          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -3560,7 +3562,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Veyrier</t>
+          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3579,7 +3581,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-veyrier/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-chene-bougeries/commercial</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3589,7 +3591,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -3606,7 +3608,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
+          <t>Locaux commerciaux à louer à Veyrier</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -3614,7 +3616,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
+          <t>Locaux commerciaux à louer à Veyrier</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3633,7 +3635,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1228-plan-les-ouates/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-veyrier/commercial</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3643,7 +3645,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -3660,7 +3662,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -3668,7 +3670,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3687,7 +3689,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1233-bernex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1228-plan-les-ouates/commercial</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3697,7 +3699,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -3714,7 +3716,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+          <t>Locaux commerciaux à louer à Bernex (1233)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3722,7 +3724,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+          <t>Locaux commerciaux à louer à Bernex (1233)</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3741,7 +3743,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1225-chene-bourg/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1233-bernex/commercial</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3751,7 +3753,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -3763,12 +3765,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>rosset</t>
+          <t>realadvisor</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>+41 21 313 43 10</t>
+          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -3776,39 +3778,93 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
+          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1225-chene-bourg/commercial</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:09:59</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>rosset</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>+41 21 313 43 10</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>+41 21 313 43 13 F. +41 21 313 43 10</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>tel: +41 21 313 43 10</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>2026-03-16 02:45:59</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>2026-03-16 16:10:21</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:09:59</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>2026-03-16 02:45:59</t>
         </is>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-03-16 02:45:59</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,26 +863,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>realadvisor</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>il y a 3 mois Naef Immobilier – Location 1 pièce • 120 m² • Arcade Rue Arnold- Winkelried 6, 1201 Genève Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year Naef Immobilier – Location Arcade à louer Rue Arnold- Winkelried</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>460</v>
-      </c>
+          <t>rosset</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>120</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>il y a 3 mois Naef Immobilier – Location 1 pièce • 120 m² • Arcade Rue Arnold- Winkelried 6, 1201 Genève Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year Naef Immobilier – Location Arcade à louer Rue Arnold- Winkelried 6, 1201 Genève Bergues - Arcade hypercentre 120m2 + 50m2 sous sol 1 pièce • 120 m² • Arcade Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year</t>
-        </is>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Plainpalais</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>1</v>
       </c>
@@ -894,85 +888,79 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/6-rue-arnold-winkelried-1201-geneve-4E56-OQNE</t>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denviron-253m%c2%b2-avec-rez-inferieur-denv-101m%c2%b2arcade-of-approx-253m%c2%b2-with-lower-ground-floor-of-approx-101m%c2%b2-plainpalais-carl-vogt-6640-6641-1-11/</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-16 20:00:43</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>realadvisor</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">il y a 1 mois Naef Immobilier – Location 206 m² • Bureau Rue Rousseau 38, 1201 Genève Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year Naef Immobilier – Location Bureau à louer Rue Rousseau 38, 1201 Genève Bureau 206m2 à louer  Genève </t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>362</v>
-      </c>
+          <t>rosset</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>206</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>il y a 1 mois Naef Immobilier – Location 206 m² • Bureau Rue Rousseau 38, 1201 Genève Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year Naef Immobilier – Location Bureau à louer Rue Rousseau 38, 1201 Genève Bureau 206m2 à louer  Genève Centre, proche de la gare Cornavin 206 m² • Bureau Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year</t>
-        </is>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Eaux-Vives</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/38-rue-rousseau-1201-geneve-QN34-7LBG</t>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denviron-388-m%c2%b2-dont-179-m%c2%b2-au-sous-solarcade-of-approx-388-m%c2%b2-179-m%c2%b2-of-which-in-the-basement-eaux-vives-1580-1581-2-13/</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-03-16 20:00:43</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
     </row>
@@ -984,26 +972,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 656 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - </t>
+          <t>il y a 3 mois Naef Immobilier – Location 1 pièce • 120 m² • Arcade Rue Arnold- Winkelried 6, 1201 Genève Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year Naef Immobilier – Location Arcade à louer Rue Arnold- Winkelried</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>947</v>
+        <v>460</v>
       </c>
       <c r="D10" t="n">
-        <v>656</v>
+        <v>120</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 656 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 656 m2 - Surface high techn et industrielle au Cur de Genève 656 m² • Commercial Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year</t>
+          <t>il y a 3 mois Naef Immobilier – Location 1 pièce • 120 m² • Arcade Rue Arnold- Winkelried 6, 1201 Genève Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year Naef Immobilier – Location Arcade à louer Rue Arnold- Winkelried 6, 1201 Genève Bergues - Arcade hypercentre 120m2 + 50m2 sous sol 1 pièce • 120 m² • Arcade Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1015,7 +1003,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-95R9-E66W</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/6-rue-arnold-winkelried-1201-geneve-4E56-OQNE</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1042,19 +1030,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 438 m² • Bureau Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year Naef Immobilier – Location Bureau à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - </t>
+          <t xml:space="preserve">il y a 1 mois Naef Immobilier – Location 206 m² • Bureau Rue Rousseau 38, 1201 Genève Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year Naef Immobilier – Location Bureau à louer Rue Rousseau 38, 1201 Genève Bureau 206m2 à louer  Genève </t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>688</v>
+        <v>362</v>
       </c>
       <c r="D11" t="n">
-        <v>438</v>
+        <v>206</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 438 m² • Bureau Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year Naef Immobilier – Location Bureau à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 438m2 - Bureaux 438 m² • Bureau Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year</t>
+          <t>il y a 1 mois Naef Immobilier – Location 206 m² • Bureau Rue Rousseau 38, 1201 Genève Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year Naef Immobilier – Location Bureau à louer Rue Rousseau 38, 1201 Genève Bureau 206m2 à louer  Genève Centre, proche de la gare Cornavin 206 m² • Bureau Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1073,7 +1061,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-XEG4-2OOX</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/38-rue-rousseau-1201-geneve-QN34-7LBG</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1100,19 +1088,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 3272 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève</t>
+          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 656 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - </t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>865</v>
+        <v>947</v>
       </c>
       <c r="D12" t="n">
-        <v>3272</v>
+        <v>656</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 3272 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 3272 m2 - Locaux Tertiaires et Secondaires au Cur de Genève 3272 m² • Commercial Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 656 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 656 m2 - Surface high techn et industrielle au Cur de Genève 656 m² • Commercial Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1131,7 +1119,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-LDX9-PVV2</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-95R9-E66W</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1158,19 +1146,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 258 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de La</t>
+          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 438 m² • Bureau Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year Naef Immobilier – Location Bureau à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - </t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>222</v>
+        <v>688</v>
       </c>
       <c r="D13" t="n">
-        <v>258</v>
+        <v>438</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 258 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de Lausanne - Bureaux de 258 m² 258 m² • Bureau Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 438 m² • Bureau Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year Naef Immobilier – Location Bureau à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 438m2 - Bureaux 438 m² • Bureau Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1189,7 +1177,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-ZZ74-D5V3</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-XEG4-2OOX</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1216,19 +1204,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 316 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 12</t>
+          <t>il y a 4 mois Naef Immobilier – Location 3272 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>522</v>
+        <v>865</v>
       </c>
       <c r="D14" t="n">
-        <v>316</v>
+        <v>3272</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 316 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureaux de 316 m² au 3ème étage 316 m² • Bureau Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 3272 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 3272 m2 - Locaux Tertiaires et Secondaires au Cur de Genève 3272 m² • Commercial Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1247,7 +1235,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-VBG4-7QXW</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-LDX9-PVV2</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1274,19 +1262,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 266 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantep</t>
+          <t>il y a 4 mois Naef Immobilier – Location 258 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de La</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>637</v>
+        <v>222</v>
       </c>
       <c r="D15" t="n">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 266 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureau de 266m² aux derniers étages 266 m² • Bureau Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 258 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de Lausanne - Bureaux de 258 m² 258 m² • Bureau Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1305,7 +1293,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-23ZJ-WQ7B</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-ZZ74-D5V3</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1332,26 +1320,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 162 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève C</t>
+          <t>il y a 4 mois Naef Immobilier – Location 316 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 12</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>276</v>
+        <v>522</v>
       </c>
       <c r="D16" t="n">
-        <v>162</v>
+        <v>316</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 162 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureau au 1er étage de 162 m² quartier dynamique 162 m² • Bureau Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 316 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureaux de 316 m² au 3ème étage 316 m² • Bureau Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1363,7 +1351,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-LDX9-PZPW</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-VBG4-7QXW</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1390,24 +1378,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade </t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>il y a 4 mois Naef Immobilier – Location 266 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantep</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>637</v>
+      </c>
       <c r="D17" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 260m2 à louer  Quartier des Charmilles, Genève 260 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 266 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureau de 266m² aux derniers étages 266 m² • Bureau Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1419,7 +1409,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-95R9-G6P5</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-23ZJ-WQ7B</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1446,28 +1436,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>il y a 4 mois Naef Immobilier – Location 162 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève C</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>276</v>
+      </c>
       <c r="D18" t="n">
-        <v>164</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Rive</t>
-        </is>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande</t>
+          <t>il y a 4 mois Naef Immobilier – Location 162 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureau au 1er étage de 162 m² quartier dynamique 162 m² • Bureau Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1479,7 +1467,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/11-cours-de-rive-1204-geneve-VBG4-7VZQ</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-LDX9-PZPW</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1501,168 +1489,156 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>realadvisor</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade c</t>
-        </is>
-      </c>
+          <t>rosset</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>130</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 130m2 à louer  Quartier des Charmilles, Genève 130 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year</t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Rive</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-XEG4-9ONV</t>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-90-m%c2%b2-au-rez-de-chausseearcade-of-approx-90-m%c2%b2-on-first-floor-rive-geneve-centre-1270-1271-2-13/</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-03-16 20:00:43</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>realadvisor</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • </t>
-        </is>
-      </c>
+          <t>rosset</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>770</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • Bureau Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year</t>
-        </is>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Plainpalais</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/rue-jean-jaquet-1201-geneve-WRG4-9WBO</t>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-80m%c2%b2-avec-depot-denv-30m%c2%b2-au-sous-solarcade-of-approx-80m%c2%b2-with-storage-area-of-approx-30m%c2%b2-in-the-base-plainpalais-820-821-1-17/</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-03-16 20:00:43</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>realadvisor</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Sur</t>
-        </is>
-      </c>
+          <t>rosset</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>1351</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Surface de 1'351 m² sur deux niveaux 1351 m² • Bureau Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande</t>
-        </is>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Plainpalais</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/7-rue-barton-1201-geneve-MXG4-NW29</t>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denviron-82-m%c2%b2-au-rez-de-chaussee82-m%c2%b2-arcade-on-ground-floor-plainpalais-9680-9681-1-13/</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-03-16 20:00:43</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
     </row>
@@ -1674,24 +1650,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genèv</t>
+          <t xml:space="preserve">il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade </t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de Lausanne - Bureaux d'env. 205 m² 205 m² • Bureau Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year</t>
+          <t>il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 260m2 à louer  Quartier des Charmilles, Genève 260 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1703,7 +1679,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-WRG4-DVXX</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-95R9-G6P5</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1730,26 +1706,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 28 jours Zimmermann Immobilier 2 pièces • 22 m² • Bureau Place De Cornavin, 1201 Genève Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year Zimmermann Immobilier Bureau à louer Place De Cornavin, 1201 Genève Bureau privatif </t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>550</v>
-      </c>
+          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>22</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
+        <v>164</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Rive</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>il y a 28 jours Zimmermann Immobilier 2 pièces • 22 m² • Bureau Place De Cornavin, 1201 Genève Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year Zimmermann Immobilier Bureau à louer Place De Cornavin, 1201 Genève Bureau privatif de 14 m² dans grand espace partagé- 14 m² - en face de la Gare Cornavin 2 pièces • 22 m² • Bureau Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1761,7 +1739,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/place-de-cornavin-1201-geneve-VBG4-9ZEO</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/11-cours-de-rive-1204-geneve-VBG4-7VZQ</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1788,26 +1766,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>il y a 1 mois Naef Immobilier – Location Bureau Rue Des Deux-Ponts 27, 1205 Genève Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178 - Naef Immobilier – Location Bureau à louer Rue Des Deux-Ponts 27, 1205 Genève Emplacement publicitaire pour une enseigne - Genève Pla</t>
+          <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade c</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Plainpalais</t>
-        </is>
-      </c>
+      <c r="D24" t="n">
+        <v>130</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>il y a 1 mois Naef Immobilier – Location Bureau Rue Des Deux-Ponts 27, 1205 Genève Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178 - Naef Immobilier – Location Bureau à louer Rue Des Deux-Ponts 27, 1205 Genève Emplacement publicitaire pour une enseigne - Genève Plainpalais Bureau Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178</t>
+          <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 130m2 à louer  Quartier des Charmilles, Genève 130 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1819,7 +1795,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/27-rue-des-deux-ponts-1205-geneve-23ZJ-9XPW</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-XEG4-9ONV</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1846,26 +1822,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Eaux-Vives - Lac</t>
+          <t xml:space="preserve">il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • </t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Eaux-Vives</t>
-        </is>
-      </c>
+      <c r="D25" t="n">
+        <v>770</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Eaux-Vives - Lac</t>
+          <t>il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • Bureau Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1877,7 +1851,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-eaux-vives-lac/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/rue-jean-jaquet-1201-geneve-WRG4-9WBO</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1904,26 +1878,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Jonction - Plainpalais</t>
+          <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Sur</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Plainpalais</t>
-        </is>
-      </c>
+      <c r="D26" t="n">
+        <v>1351</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Jonction - Plainpalais</t>
+          <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Surface de 1'351 m² sur deux niveaux 1351 m² • Bureau Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1935,7 +1907,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-jonction-plainpalais/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/7-rue-barton-1201-geneve-MXG4-NW29</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1962,26 +1934,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Champel - Roseraie</t>
+          <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genèv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Champel</t>
-        </is>
-      </c>
+      <c r="D27" t="n">
+        <v>205</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Champel - Roseraie</t>
+          <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de Lausanne - Bureaux d'env. 205 m² 205 m² • Bureau Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1993,7 +1963,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-champel-roseraie/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-WRG4-DVXX</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2020,26 +1990,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>il y a 2 mois NSR-Group S.A Garage Chemin de Roches, 1207 Genève Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400 - NSR-Group S.A Garage à louer Chemin de Roches, 1207 Genève Eaux-Vives - Box zu vermieten Garage Emplacement facilement accessible Portail de</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Eaux-Vives</t>
-        </is>
-      </c>
+          <t xml:space="preserve">il y a 28 jours Zimmermann Immobilier 2 pièces • 22 m² • Bureau Place De Cornavin, 1201 Genève Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year Zimmermann Immobilier Bureau à louer Place De Cornavin, 1201 Genève Bureau privatif </t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>550</v>
+      </c>
+      <c r="D28" t="n">
+        <v>22</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>il y a 2 mois NSR-Group S.A Garage Chemin de Roches, 1207 Genève Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400 - NSR-Group S.A Garage à louer Chemin de Roches, 1207 Genève Eaux-Vives - Box zu vermieten Garage Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400</t>
+          <t>il y a 28 jours Zimmermann Immobilier 2 pièces • 22 m² • Bureau Place De Cornavin, 1201 Genève Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year Zimmermann Immobilier Bureau à louer Place De Cornavin, 1201 Genève Bureau privatif de 14 m² dans grand espace partagé- 14 m² - en face de la Gare Cornavin 2 pièces • 22 m² • Bureau Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2051,7 +2021,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/chemin-de-roches-1207-geneve-8VBP-BWZW</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/place-de-cornavin-1201-geneve-VBG4-9ZEO</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2061,12 +2031,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2078,24 +2048,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA Bureau 1203 Genève 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000 - Segimo SA Bureau à louer 1203 Genève Coworking professionnel pour architecte dans les locaux d'un promoteur immobilier à 1203 Genève Bureau 35 m² entièrement rénovés Cui</t>
+          <t>il y a 1 mois Naef Immobilier – Location Bureau Rue Des Deux-Ponts 27, 1205 Genève Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178 - Naef Immobilier – Location Bureau à louer Rue Des Deux-Ponts 27, 1205 Genève Emplacement publicitaire pour une enseigne - Genève Pla</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="n">
-        <v>35</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Plainpalais</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA Bureau 1203 Genève 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000 - Segimo SA Bureau à louer 1203 Genève Coworking professionnel pour architecte dans les locaux d'un promoteur immobilier à 1203 Genève Bureau 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000</t>
+          <t>il y a 1 mois Naef Immobilier – Location Bureau Rue Des Deux-Ponts 27, 1205 Genève Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178 - Naef Immobilier – Location Bureau à louer Rue Des Deux-Ponts 27, 1205 Genève Emplacement publicitaire pour une enseigne - Genève Plainpalais Bureau Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2107,12 +2079,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-KQNL-GWW5</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/27-rue-des-deux-ponts-1205-geneve-23ZJ-9XPW</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2134,24 +2106,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>il y a 4 heures Segimo SA 35 m² • Bureau 1203 Genève Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande - Segimo SA Bureau à louer 1203 Genève 35 m² • Bureau Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande</t>
+          <t>Locaux commerciaux à louer à Eaux-Vives - Lac</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="n">
-        <v>35</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Eaux-Vives</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>il y a 4 heures Segimo SA 35 m² • Bureau 1203 Genève Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande - Segimo SA Bureau à louer 1203 Genève 35 m² • Bureau Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande</t>
+          <t>Locaux commerciaux à louer à Eaux-Vives - Lac</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2163,12 +2137,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-8OOA-XD6Z</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-eaux-vives-lac/commercial</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2190,24 +2164,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
+          <t>Locaux commerciaux à louer à Jonction - Plainpalais</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="n">
-        <v>35</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Plainpalais</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
+          <t>Locaux commerciaux à louer à Jonction - Plainpalais</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2219,7 +2195,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-Y235-5V7W</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-jonction-plainpalais/commercial</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2229,12 +2205,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2246,22 +2222,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Local commercial</t>
+          <t>Locaux commerciaux à louer à Champel - Roseraie</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Champel</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Local commercial</t>
+          <t>Locaux commerciaux à louer à Champel - Roseraie</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -2273,7 +2253,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-champel-roseraie/commercial</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2300,22 +2280,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Canton de Genève</t>
+          <t>il y a 2 mois NSR-Group S.A Garage Chemin de Roches, 1207 Genève Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400 - NSR-Group S.A Garage à louer Chemin de Roches, 1207 Genève Eaux-Vives - Box zu vermieten Garage Emplacement facilement accessible Portail de</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Eaux-Vives</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Canton de Genève</t>
+          <t>il y a 2 mois NSR-Group S.A Garage Chemin de Roches, 1207 Genève Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400 - NSR-Group S.A Garage à louer Chemin de Roches, 1207 Genève Eaux-Vives - Box zu vermieten Garage Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -2327,7 +2311,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/canton-geneve/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/chemin-de-roches-1207-geneve-8VBP-BWZW</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2337,12 +2321,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-03-16 20:00:43</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
     </row>
@@ -2354,22 +2338,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer</t>
+          <t>il y a 3 jours Segimo SA Bureau 1203 Genève 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000 - Segimo SA Bureau à louer 1203 Genève Coworking professionnel pour architecte dans les locaux d'un promoteur immobilier à 1203 Genève Bureau 35 m² entièrement rénovés Cui</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>35</v>
+      </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer</t>
+          <t>il y a 3 jours Segimo SA Bureau 1203 Genève 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000 - Segimo SA Bureau à louer 1203 Genève Coworking professionnel pour architecte dans les locaux d'un promoteur immobilier à 1203 Genève Bureau 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2381,12 +2367,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-geneve/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-KQNL-GWW5</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2408,22 +2394,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
+          <t>il y a 4 heures Segimo SA 35 m² • Bureau 1203 Genève Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande - Segimo SA Bureau à louer 1203 Genève 35 m² • Bureau Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>35</v>
+      </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
+          <t>il y a 4 heures Segimo SA 35 m² • Bureau 1203 Genève Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande - Segimo SA Bureau à louer 1203 Genève 35 m² • Bureau Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -2435,12 +2423,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-bouchet-moillebeau/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-8OOA-XD6Z</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2462,22 +2450,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
+          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>35</v>
+      </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
+          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2489,7 +2479,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-cluse-philosophes/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-Y235-5V7W</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2499,12 +2489,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-03-16 20:00:43</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2506,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
+          <t>Local commercial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -2524,7 +2514,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
+          <t>Local commercial</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2543,7 +2533,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-grand-pre-vermont/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2570,7 +2560,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
+          <t>Canton de Genève</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -2578,7 +2568,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
+          <t>Canton de Genève</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2597,7 +2587,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-st-gervais-chantepoulet/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/canton-geneve/commercial</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2624,7 +2614,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
+          <t>Locaux commerciaux à louer</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -2632,7 +2622,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
+          <t>Locaux commerciaux à louer</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2651,7 +2641,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-paquis-navigation/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-geneve/commercial</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2678,7 +2668,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à ONU - Rigot</t>
+          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2686,7 +2676,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à ONU - Rigot</t>
+          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2705,7 +2695,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-onu-rigot/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-bouchet-moillebeau/commercial</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2732,7 +2722,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
+          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2740,7 +2730,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
+          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2759,7 +2749,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-secheron-prieure/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-cluse-philosophes/commercial</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2786,7 +2776,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cité - Centre</t>
+          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -2794,7 +2784,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cité - Centre</t>
+          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2813,7 +2803,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-cite-centre/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-grand-pre-vermont/commercial</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2840,7 +2830,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
+          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -2848,7 +2838,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
+          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2867,7 +2857,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-charmilles-chatelaine/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-st-gervais-chantepoulet/commercial</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2894,7 +2884,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
+          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -2902,7 +2892,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
+          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2921,7 +2911,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-st-jean-aire/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-paquis-navigation/commercial</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2948,7 +2938,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
+          <t>Locaux commerciaux à louer à ONU - Rigot</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -2956,7 +2946,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
+          <t>Locaux commerciaux à louer à ONU - Rigot</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2975,7 +2965,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-florissant-malagnou/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-onu-rigot/commercial</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3002,19 +2992,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
+          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Acacias</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
+          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3033,7 +3019,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-batie-acacias/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-secheron-prieure/commercial</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3060,7 +3046,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Délices - Grottes</t>
+          <t>Locaux commerciaux à louer à Cité - Centre</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -3068,7 +3054,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Délices - Grottes</t>
+          <t>Locaux commerciaux à louer à Cité - Centre</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3087,7 +3073,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-delices-grottes/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-cite-centre/commercial</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3114,19 +3100,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
+          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Acacias</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
+          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3145,7 +3127,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1227-les-acacias/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-charmilles-chatelaine/commercial</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3172,7 +3154,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Vernier</t>
+          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -3180,7 +3162,7 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Vernier</t>
+          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3199,7 +3181,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-vernier/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-st-jean-aire/commercial</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3226,7 +3208,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Lancy</t>
+          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -3234,7 +3216,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Lancy</t>
+          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3253,7 +3235,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-lancy/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-florissant-malagnou/commercial</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3280,15 +3262,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Meyrin</t>
+          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Acacias</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Meyrin</t>
+          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3307,7 +3293,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-meyrin/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-batie-acacias/commercial</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3334,19 +3320,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
+          <t>Locaux commerciaux à louer à Délices - Grottes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Carouge</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
+          <t>Locaux commerciaux à louer à Délices - Grottes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3365,7 +3347,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1227-carouge-ge/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-delices-grottes/commercial</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3392,15 +3374,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Onex (1213)</t>
+          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Acacias</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Onex (1213)</t>
+          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3419,7 +3405,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1213-onex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1227-les-acacias/commercial</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3446,7 +3432,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Thônex (1226)</t>
+          <t>Locaux commerciaux à louer à Vernier</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -3454,7 +3440,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Thônex (1226)</t>
+          <t>Locaux commerciaux à louer à Vernier</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3473,7 +3459,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1226-thonex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-vernier/commercial</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3500,7 +3486,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
+          <t>Locaux commerciaux à louer à Lancy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -3508,7 +3494,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
+          <t>Locaux commerciaux à louer à Lancy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3527,7 +3513,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-le-grand-saconnex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-lancy/commercial</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3554,7 +3540,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
+          <t>Locaux commerciaux à louer à Meyrin</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -3562,7 +3548,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
+          <t>Locaux commerciaux à louer à Meyrin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3581,7 +3567,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-chene-bougeries/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-meyrin/commercial</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3608,15 +3594,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Veyrier</t>
+          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Carouge</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Veyrier</t>
+          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3635,7 +3625,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-veyrier/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1227-carouge-ge/commercial</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3662,7 +3652,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
+          <t>Locaux commerciaux à louer à Onex (1213)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -3670,7 +3660,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
+          <t>Locaux commerciaux à louer à Onex (1213)</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3689,7 +3679,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1228-plan-les-ouates/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1213-onex/commercial</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3716,7 +3706,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+          <t>Locaux commerciaux à louer à Thônex (1226)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3724,7 +3714,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+          <t>Locaux commerciaux à louer à Thônex (1226)</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3743,7 +3733,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1233-bernex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1226-thonex/commercial</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3770,7 +3760,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -3778,7 +3768,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3797,7 +3787,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1225-chene-bourg/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-le-grand-saconnex/commercial</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3819,12 +3809,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>rosset</t>
+          <t>realadvisor</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>+41 21 313 43 10</t>
+          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -3832,39 +3822,309 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
+          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/ville-chene-bougeries/commercial</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:09:59</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-03-16 20:00:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>realadvisor</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Locaux commerciaux à louer à Veyrier</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Locaux commerciaux à louer à Veyrier</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/ville-veyrier/commercial</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:09:59</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2026-03-16 20:00:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>realadvisor</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1228-plan-les-ouates/commercial</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:09:59</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2026-03-16 20:00:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>realadvisor</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1233-bernex/commercial</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:09:59</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2026-03-16 20:00:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>realadvisor</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1225-chene-bourg/commercial</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:09:59</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2026-03-16 20:00:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>rosset</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>+41 21 313 43 10</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>+41 21 313 43 13 F. +41 21 313 43 10</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>tel: +41 21 313 43 10</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>2026-03-16 02:45:59</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:09:59</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
+          <t>2026-03-16 23:30:57</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
+          <t>2026-03-16 23:30:57</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
+          <t>2026-03-16 23:30:57</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
+          <t>2026-03-16 23:30:57</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
+          <t>2026-03-16 23:30:57</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N66"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16 23:30:57</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16 23:30:57</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16 23:30:57</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16 23:30:57</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16 23:30:57</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1645,24 +1645,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>realadvisor</t>
+          <t>pilet_renaud</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade </t>
+          <t>ACACIAS - CHF 374.-/m2 - Arcade d'environ 72m² Jonction-Plainpalais-Arve Rive, Les Acacias Loyer CHF 2’245.-</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>260</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 260m2 à louer  Quartier des Charmilles, Genève 260 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year</t>
-        </is>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Rive</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>1</v>
       </c>
@@ -1674,27 +1674,27 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-95R9-G6P5</t>
+          <t>https://www.pilet-renaud.ch/fr/a-louer//acacias-chf-374-m2-arcade-denviron-72m--8598</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-03-16 20:00:43</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
     </row>
@@ -1706,28 +1706,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système </t>
+          <t xml:space="preserve">il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade </t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>164</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Rive</t>
-        </is>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande</t>
+          <t>il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 260m2 à louer  Quartier des Charmilles, Genève 260 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1739,7 +1735,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/11-cours-de-rive-1204-geneve-VBG4-7VZQ</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-95R9-G6P5</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1766,24 +1762,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade c</t>
+          <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système </t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>130</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
+        <v>164</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Rive</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 130m2 à louer  Quartier des Charmilles, Genève 130 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year</t>
+          <t>il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-XEG4-9ONV</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/11-cours-de-rive-1204-geneve-VBG4-7VZQ</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1822,24 +1822,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • </t>
+          <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade c</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
-        <v>770</v>
+        <v>130</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • Bureau Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year</t>
+          <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 130m2 à louer  Quartier des Charmilles, Genève 130 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/rue-jean-jaquet-1201-geneve-WRG4-9WBO</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-XEG4-9ONV</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1873,26 +1873,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>realadvisor</t>
+          <t>pilet_renaud</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Sur</t>
+          <t>Estimer</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>1351</v>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Surface de 1'351 m² sur deux niveaux 1351 m² • Bureau Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Champel</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>35</v>
@@ -1902,53 +1902,53 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/7-rue-barton-1201-geneve-MXG4-NW29</t>
+          <t>https://www.pilet-renaud.ch/fr/accueil/estimer</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-03-16 20:00:43</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>realadvisor</t>
+          <t>pilet_renaud</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genèv</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>205</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de Lausanne - Bureaux d'env. 205 m² 205 m² • Bureau Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Champel</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
         <v>35</v>
@@ -1958,27 +1958,27 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-WRG4-DVXX</t>
+          <t>https://www.pilet-renaud.ch/fr/accueil/contact</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-03-16 20:00:43</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
     </row>
@@ -1990,26 +1990,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">il y a 28 jours Zimmermann Immobilier 2 pièces • 22 m² • Bureau Place De Cornavin, 1201 Genève Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year Zimmermann Immobilier Bureau à louer Place De Cornavin, 1201 Genève Bureau privatif </t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>550</v>
-      </c>
+          <t xml:space="preserve">il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • </t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>22</v>
+        <v>770</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>il y a 28 jours Zimmermann Immobilier 2 pièces • 22 m² • Bureau Place De Cornavin, 1201 Genève Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year Zimmermann Immobilier Bureau à louer Place De Cornavin, 1201 Genève Bureau privatif de 14 m² dans grand espace partagé- 14 m² - en face de la Gare Cornavin 2 pièces • 22 m² • Bureau Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year</t>
+          <t>il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • Bureau Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2021,7 +2019,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/place-de-cornavin-1201-geneve-VBG4-9ZEO</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/rue-jean-jaquet-1201-geneve-WRG4-9WBO</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2048,26 +2046,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>il y a 1 mois Naef Immobilier – Location Bureau Rue Des Deux-Ponts 27, 1205 Genève Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178 - Naef Immobilier – Location Bureau à louer Rue Des Deux-Ponts 27, 1205 Genève Emplacement publicitaire pour une enseigne - Genève Pla</t>
+          <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Sur</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Plainpalais</t>
-        </is>
-      </c>
+      <c r="D29" t="n">
+        <v>1351</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>il y a 1 mois Naef Immobilier – Location Bureau Rue Des Deux-Ponts 27, 1205 Genève Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178 - Naef Immobilier – Location Bureau à louer Rue Des Deux-Ponts 27, 1205 Genève Emplacement publicitaire pour une enseigne - Genève Plainpalais Bureau Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178</t>
+          <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Surface de 1'351 m² sur deux niveaux 1351 m² • Bureau Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2079,7 +2075,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/27-rue-des-deux-ponts-1205-geneve-23ZJ-9XPW</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/7-rue-barton-1201-geneve-MXG4-NW29</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2106,26 +2102,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Eaux-Vives - Lac</t>
+          <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genèv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Eaux-Vives</t>
-        </is>
-      </c>
+      <c r="D30" t="n">
+        <v>205</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Eaux-Vives - Lac</t>
+          <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de Lausanne - Bureaux d'env. 205 m² 205 m² • Bureau Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2137,7 +2131,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-eaux-vives-lac/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-WRG4-DVXX</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2164,26 +2158,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Jonction - Plainpalais</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Plainpalais</t>
-        </is>
-      </c>
+          <t xml:space="preserve">il y a 28 jours Zimmermann Immobilier 2 pièces • 22 m² • Bureau Place De Cornavin, 1201 Genève Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year Zimmermann Immobilier Bureau à louer Place De Cornavin, 1201 Genève Bureau privatif </t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>550</v>
+      </c>
+      <c r="D31" t="n">
+        <v>22</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Jonction - Plainpalais</t>
+          <t>il y a 28 jours Zimmermann Immobilier 2 pièces • 22 m² • Bureau Place De Cornavin, 1201 Genève Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year Zimmermann Immobilier Bureau à louer Place De Cornavin, 1201 Genève Bureau privatif de 14 m² dans grand espace partagé- 14 m² - en face de la Gare Cornavin 2 pièces • 22 m² • Bureau Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2195,7 +2189,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-jonction-plainpalais/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/place-de-cornavin-1201-geneve-VBG4-9ZEO</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2222,19 +2216,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Champel - Roseraie</t>
+          <t>il y a 1 mois Naef Immobilier – Location Bureau Rue Des Deux-Ponts 27, 1205 Genève Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178 - Naef Immobilier – Location Bureau à louer Rue Des Deux-Ponts 27, 1205 Genève Emplacement publicitaire pour une enseigne - Genève Pla</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Champel</t>
+          <t>Plainpalais</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Champel - Roseraie</t>
+          <t>il y a 1 mois Naef Immobilier – Location Bureau Rue Des Deux-Ponts 27, 1205 Genève Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178 - Naef Immobilier – Location Bureau à louer Rue Des Deux-Ponts 27, 1205 Genève Emplacement publicitaire pour une enseigne - Genève Plainpalais Bureau Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2253,7 +2247,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-champel-roseraie/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/27-rue-des-deux-ponts-1205-geneve-23ZJ-9XPW</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2280,7 +2274,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>il y a 2 mois NSR-Group S.A Garage Chemin de Roches, 1207 Genève Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400 - NSR-Group S.A Garage à louer Chemin de Roches, 1207 Genève Eaux-Vives - Box zu vermieten Garage Emplacement facilement accessible Portail de</t>
+          <t>Locaux commerciaux à louer à Eaux-Vives - Lac</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -2292,7 +2286,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>il y a 2 mois NSR-Group S.A Garage Chemin de Roches, 1207 Genève Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400 - NSR-Group S.A Garage à louer Chemin de Roches, 1207 Genève Eaux-Vives - Box zu vermieten Garage Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400</t>
+          <t>Locaux commerciaux à louer à Eaux-Vives - Lac</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2311,7 +2305,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/chemin-de-roches-1207-geneve-8VBP-BWZW</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-eaux-vives-lac/commercial</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2321,12 +2315,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16 10:10:13</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-03-16 13:22:39</t>
+          <t>2026-03-16 20:00:43</t>
         </is>
       </c>
     </row>
@@ -2338,24 +2332,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA Bureau 1203 Genève 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000 - Segimo SA Bureau à louer 1203 Genève Coworking professionnel pour architecte dans les locaux d'un promoteur immobilier à 1203 Genève Bureau 35 m² entièrement rénovés Cui</t>
+          <t>Locaux commerciaux à louer à Jonction - Plainpalais</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="n">
-        <v>35</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Plainpalais</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA Bureau 1203 Genève 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000 - Segimo SA Bureau à louer 1203 Genève Coworking professionnel pour architecte dans les locaux d'un promoteur immobilier à 1203 Genève Bureau 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000</t>
+          <t>Locaux commerciaux à louer à Jonction - Plainpalais</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2367,12 +2363,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-KQNL-GWW5</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-jonction-plainpalais/commercial</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-16 16:10:21</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2394,24 +2390,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>il y a 4 heures Segimo SA 35 m² • Bureau 1203 Genève Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande - Segimo SA Bureau à louer 1203 Genève 35 m² • Bureau Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande</t>
+          <t>Locaux commerciaux à louer à Champel - Roseraie</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="n">
-        <v>35</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Champel</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>il y a 4 heures Segimo SA 35 m² • Bureau 1203 Genève Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande - Segimo SA Bureau à louer 1203 Genève 35 m² • Bureau Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande</t>
+          <t>Locaux commerciaux à louer à Champel - Roseraie</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -2423,12 +2421,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-8OOA-XD6Z</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-champel-roseraie/commercial</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2450,24 +2448,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
+          <t>il y a 2 mois NSR-Group S.A Garage Chemin de Roches, 1207 Genève Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400 - NSR-Group S.A Garage à louer Chemin de Roches, 1207 Genève Eaux-Vives - Box zu vermieten Garage Emplacement facilement accessible Portail de</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="n">
-        <v>35</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Eaux-Vives</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
+          <t>il y a 2 mois NSR-Group S.A Garage Chemin de Roches, 1207 Genève Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400 - NSR-Group S.A Garage à louer Chemin de Roches, 1207 Genève Eaux-Vives - Box zu vermieten Garage Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-Y235-5V7W</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/chemin-de-roches-1207-geneve-8VBP-BWZW</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
+          <t>2026-03-16 10:10:13</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>2026-03-16 13:22:39</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
     </row>
@@ -2506,22 +2506,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Local commercial</t>
+          <t>il y a 3 jours Segimo SA Bureau 1203 Genève 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000 - Segimo SA Bureau à louer 1203 Genève Coworking professionnel pour architecte dans les locaux d'un promoteur immobilier à 1203 Genève Bureau 35 m² entièrement rénovés Cui</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>35</v>
+      </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Local commercial</t>
+          <t>il y a 3 jours Segimo SA Bureau 1203 Genève 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000 - Segimo SA Bureau à louer 1203 Genève Coworking professionnel pour architecte dans les locaux d'un promoteur immobilier à 1203 Genève Bureau 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -2533,12 +2535,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-KQNL-GWW5</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2560,22 +2562,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Canton de Genève</t>
+          <t>il y a 4 heures Segimo SA 35 m² • Bureau 1203 Genève Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande - Segimo SA Bureau à louer 1203 Genève 35 m² • Bureau Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>35</v>
+      </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Canton de Genève</t>
+          <t>il y a 4 heures Segimo SA 35 m² • Bureau 1203 Genève Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande - Segimo SA Bureau à louer 1203 Genève 35 m² • Bureau Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2587,12 +2591,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/canton-geneve/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-8OOA-XD6Z</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-03-15 23:33:16</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2614,22 +2618,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer</t>
+          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>35</v>
+      </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer</t>
+          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2641,7 +2647,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-geneve/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-Y235-5V7W</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2651,12 +2657,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-16 19:09:59</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-03-16 20:00:43</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2674,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
+          <t>Local commercial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2676,7 +2682,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
+          <t>Local commercial</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2695,7 +2701,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-bouchet-moillebeau/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/commercial</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2722,7 +2728,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
+          <t>Canton de Genève</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2730,7 +2736,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
+          <t>Canton de Genève</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2749,7 +2755,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-cluse-philosophes/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/canton-geneve/commercial</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2776,7 +2782,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
+          <t>Locaux commerciaux à louer</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -2784,7 +2790,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
+          <t>Locaux commerciaux à louer</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2803,7 +2809,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-grand-pre-vermont/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-geneve/commercial</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2830,7 +2836,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
+          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -2838,7 +2844,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
+          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2857,7 +2863,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-st-gervais-chantepoulet/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-bouchet-moillebeau/commercial</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2884,7 +2890,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
+          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -2892,7 +2898,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
+          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2911,7 +2917,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-paquis-navigation/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-cluse-philosophes/commercial</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2938,7 +2944,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à ONU - Rigot</t>
+          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -2946,7 +2952,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à ONU - Rigot</t>
+          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2965,7 +2971,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-onu-rigot/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-grand-pre-vermont/commercial</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2992,7 +2998,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
+          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -3000,7 +3006,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
+          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3019,7 +3025,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-secheron-prieure/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-st-gervais-chantepoulet/commercial</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3046,7 +3052,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cité - Centre</t>
+          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -3054,7 +3060,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Cité - Centre</t>
+          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3073,7 +3079,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-cite-centre/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-paquis-navigation/commercial</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3100,7 +3106,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
+          <t>Locaux commerciaux à louer à ONU - Rigot</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -3108,7 +3114,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
+          <t>Locaux commerciaux à louer à ONU - Rigot</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3127,7 +3133,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-charmilles-chatelaine/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-onu-rigot/commercial</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3154,7 +3160,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
+          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -3162,7 +3168,7 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
+          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3181,7 +3187,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-st-jean-aire/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-secheron-prieure/commercial</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3208,7 +3214,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
+          <t>Locaux commerciaux à louer à Cité - Centre</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -3216,7 +3222,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
+          <t>Locaux commerciaux à louer à Cité - Centre</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3235,7 +3241,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-florissant-malagnou/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-cite-centre/commercial</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3262,19 +3268,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
+          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Acacias</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
+          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3293,7 +3295,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-batie-acacias/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-charmilles-chatelaine/commercial</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3320,7 +3322,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Délices - Grottes</t>
+          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -3328,7 +3330,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Délices - Grottes</t>
+          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3347,7 +3349,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-delices-grottes/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-st-jean-aire/commercial</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3374,19 +3376,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
+          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Acacias</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
+          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3405,7 +3403,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1227-les-acacias/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-florissant-malagnou/commercial</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3432,15 +3430,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Vernier</t>
+          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Acacias</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Vernier</t>
+          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3459,7 +3461,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-vernier/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-batie-acacias/commercial</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3486,7 +3488,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Lancy</t>
+          <t>Locaux commerciaux à louer à Délices - Grottes</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -3494,7 +3496,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Lancy</t>
+          <t>Locaux commerciaux à louer à Délices - Grottes</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3513,7 +3515,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-lancy/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/quartier-delices-grottes/commercial</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3540,15 +3542,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Meyrin</t>
+          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Acacias</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Meyrin</t>
+          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3567,7 +3573,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-meyrin/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1227-les-acacias/commercial</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3594,19 +3600,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
+          <t>Locaux commerciaux à louer à Vernier</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Carouge</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
+          <t>Locaux commerciaux à louer à Vernier</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3625,7 +3627,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1227-carouge-ge/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-vernier/commercial</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3652,7 +3654,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Onex (1213)</t>
+          <t>Locaux commerciaux à louer à Lancy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -3660,7 +3662,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Onex (1213)</t>
+          <t>Locaux commerciaux à louer à Lancy</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3679,7 +3681,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1213-onex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-lancy/commercial</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3706,7 +3708,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Thônex (1226)</t>
+          <t>Locaux commerciaux à louer à Meyrin</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3714,7 +3716,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Thônex (1226)</t>
+          <t>Locaux commerciaux à louer à Meyrin</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3733,7 +3735,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1226-thonex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-meyrin/commercial</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -3760,15 +3762,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
+          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Carouge</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
+          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3787,7 +3793,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-le-grand-saconnex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1227-carouge-ge/commercial</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -3814,7 +3820,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
+          <t>Locaux commerciaux à louer à Onex (1213)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -3822,7 +3828,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
+          <t>Locaux commerciaux à louer à Onex (1213)</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3841,7 +3847,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-chene-bougeries/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1213-onex/commercial</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3868,7 +3874,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Veyrier</t>
+          <t>Locaux commerciaux à louer à Thônex (1226)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -3876,7 +3882,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Veyrier</t>
+          <t>Locaux commerciaux à louer à Thônex (1226)</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3895,7 +3901,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-veyrier/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/1226-thonex/commercial</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -3922,7 +3928,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
+          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -3930,7 +3936,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
+          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3949,7 +3955,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1228-plan-les-ouates/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-le-grand-saconnex/commercial</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -3976,7 +3982,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -3984,7 +3990,7 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -4003,7 +4009,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1233-bernex/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-chene-bougeries/commercial</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4030,7 +4036,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+          <t>Locaux commerciaux à louer à Veyrier</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -4038,7 +4044,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+          <t>Locaux commerciaux à louer à Veyrier</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -4057,7 +4063,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1225-chene-bourg/commercial</t>
+          <t>https://realadvisor.ch/fr/louer/ville-veyrier/commercial</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4079,12 +4085,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>rosset</t>
+          <t>realadvisor</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>+41 21 313 43 10</t>
+          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -4092,39 +4098,201 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
+          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1228-plan-les-ouates/commercial</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:09:59</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2026-03-16 20:00:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>realadvisor</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Locaux commerciaux à louer à Bernex (1233)</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1233-bernex/commercial</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:09:59</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>2026-03-16 20:00:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>realadvisor</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1225-chene-bourg/commercial</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-03-15 23:33:16</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:09:59</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>2026-03-16 20:00:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>rosset</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>+41 21 313 43 10</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>+41 21 313 43 13 F. +41 21 313 43 10</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>tel: +41 21 313 43 10</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>2026-03-16 02:45:59</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:09:59</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-17 02:30:19</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-17 02:30:19</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-17 02:30:19</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-17 02:30:19</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-17 02:30:19</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-17 02:30:19</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-17 02:30:19</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-17 02:30:19</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-17 02:30:19</t>
+          <t>2026-03-17 04:56:15</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-17 02:30:19</t>
+          <t>2026-03-17 04:56:15</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17 02:30:19</t>
+          <t>2026-03-17 04:56:15</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-17 02:30:19</t>
+          <t>2026-03-17 04:56:15</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-17 02:30:19</t>
+          <t>2026-03-17 04:56:15</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-17 02:30:19</t>
+          <t>2026-03-17 04:56:15</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17 02:30:19</t>
+          <t>2026-03-17 04:56:15</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17 02:30:19</t>
+          <t>2026-03-17 04:56:15</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-17 04:56:15</t>
+          <t>2026-03-17 07:11:30</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-17 04:56:15</t>
+          <t>2026-03-17 07:11:30</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17 04:56:15</t>
+          <t>2026-03-17 07:11:30</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-17 04:56:15</t>
+          <t>2026-03-17 07:11:30</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-17 04:56:15</t>
+          <t>2026-03-17 07:11:30</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-17 04:56:15</t>
+          <t>2026-03-17 07:11:30</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17 04:56:15</t>
+          <t>2026-03-17 07:11:30</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17 04:56:15</t>
+          <t>2026-03-17 07:11:30</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-17 07:11:30</t>
+          <t>2026-03-17 09:59:53</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-17 07:11:30</t>
+          <t>2026-03-17 09:59:53</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17 07:11:30</t>
+          <t>2026-03-17 09:59:53</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-17 07:11:30</t>
+          <t>2026-03-17 09:59:53</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-17 07:11:30</t>
+          <t>2026-03-17 09:59:53</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-17 07:11:30</t>
+          <t>2026-03-17 09:59:53</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17 07:11:30</t>
+          <t>2026-03-17 09:59:53</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17 07:11:30</t>
+          <t>2026-03-17 09:59:53</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-17 09:59:53</t>
+          <t>2026-03-17 13:21:29</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-17 09:59:53</t>
+          <t>2026-03-17 13:21:29</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17 09:59:53</t>
+          <t>2026-03-17 13:21:29</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-17 09:59:53</t>
+          <t>2026-03-17 13:21:29</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-17 09:59:53</t>
+          <t>2026-03-17 13:21:29</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-17 09:59:53</t>
+          <t>2026-03-17 13:21:29</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17 09:59:53</t>
+          <t>2026-03-17 13:21:29</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17 09:59:53</t>
+          <t>2026-03-17 13:21:29</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-17 13:21:29</t>
+          <t>2026-03-17 16:10:09</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-17 13:21:29</t>
+          <t>2026-03-17 16:10:09</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17 13:21:29</t>
+          <t>2026-03-17 16:10:09</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-17 13:21:29</t>
+          <t>2026-03-17 16:10:09</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-17 13:21:29</t>
+          <t>2026-03-17 16:10:09</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-17 13:21:29</t>
+          <t>2026-03-17 16:10:09</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17 13:21:29</t>
+          <t>2026-03-17 16:10:09</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17 13:21:29</t>
+          <t>2026-03-17 16:10:09</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
+          <t>2026-03-17 19:08:46</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
+          <t>2026-03-17 19:08:46</t>
         </is>
       </c>
     </row>
@@ -1489,13 +1489,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rosset</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>pilet_renaud</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ACACIAS - CHF 374.-/m2 - Arcade d'environ 72m² Jonction-Plainpalais-Arve Rive, Les Acacias Loyer CHF 2’245.-</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1519,22 +1523,22 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-90-m%c2%b2-au-rez-de-chausseearcade-of-approx-90-m%c2%b2-on-first-floor-rive-geneve-centre-1270-1271-2-13/</t>
+          <t>https://www.pilet-renaud.ch/fr/a-louer//acacias-chf-374-m2-arcade-denviron-72m--8598</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17 16:10:09</t>
+          <t>2026-03-17 19:08:46</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
     </row>
@@ -1547,11 +1551,11 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Plainpalais</t>
+          <t>Rive</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1566,12 +1570,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-80m%c2%b2-avec-depot-denv-30m%c2%b2-au-sous-solarcade-of-approx-80m%c2%b2-with-storage-area-of-approx-30m%c2%b2-in-the-base-plainpalais-820-821-1-17/</t>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-90-m%c2%b2-au-rez-de-chausseearcade-of-approx-90-m%c2%b2-on-first-floor-rive-geneve-centre-1270-1271-2-13/</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1586,7 +1590,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
+          <t>2026-03-17 19:08:46</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1603,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1618,12 +1622,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denviron-82-m%c2%b2-au-rez-de-chaussee82-m%c2%b2-arcade-on-ground-floor-plainpalais-9680-9681-1-13/</t>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-80m%c2%b2-avec-depot-denv-30m%c2%b2-au-sous-solarcade-of-approx-80m%c2%b2-with-storage-area-of-approx-30m%c2%b2-in-the-base-plainpalais-820-821-1-17/</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1638,28 +1642,24 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
+          <t>2026-03-17 19:08:46</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pilet_renaud</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ACACIAS - CHF 374.-/m2 - Arcade d'environ 72m² Jonction-Plainpalais-Arve Rive, Les Acacias Loyer CHF 2’245.-</t>
-        </is>
-      </c>
+          <t>rosset</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rive</t>
+          <t>Plainpalais</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1674,17 +1674,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.pilet-renaud.ch/fr/a-louer//acacias-chf-374-m2-arcade-denviron-72m--8598</t>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denviron-82-m%c2%b2-au-rez-de-chaussee82-m%c2%b2-arcade-on-ground-floor-plainpalais-9680-9681-1-13/</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-17 19:08:46</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17 16:10:09</t>
+          <t>2026-03-17 19:08:46</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17 16:10:09</t>
+          <t>2026-03-17 19:08:46</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-17 16:10:09</t>
+          <t>2026-03-17 21:42:39</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-17 19:08:46</t>
+          <t>2026-03-17 21:42:39</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-17 16:10:09</t>
+          <t>2026-03-17 21:42:39</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-03-17 19:08:46</t>
+          <t>2026-03-17 21:42:39</t>
         </is>
       </c>
     </row>
@@ -1489,17 +1489,13 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pilet_renaud</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ACACIAS - CHF 374.-/m2 - Arcade d'environ 72m² Jonction-Plainpalais-Arve Rive, Les Acacias Loyer CHF 2’245.-</t>
-        </is>
-      </c>
+          <t>rosset</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1523,22 +1519,22 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.pilet-renaud.ch/fr/a-louer//acacias-chf-374-m2-arcade-denviron-72m--8598</t>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-90-m%c2%b2-au-rez-de-chausseearcade-of-approx-90-m%c2%b2-on-first-floor-rive-geneve-centre-1270-1271-2-13/</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17 19:08:46</t>
+          <t>2026-03-17 21:42:39</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-17 21:42:39</t>
         </is>
       </c>
     </row>
@@ -1551,11 +1547,11 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rive</t>
+          <t>Plainpalais</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1570,12 +1566,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-90-m%c2%b2-au-rez-de-chausseearcade-of-approx-90-m%c2%b2-on-first-floor-rive-geneve-centre-1270-1271-2-13/</t>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-80m%c2%b2-avec-depot-denv-30m%c2%b2-au-sous-solarcade-of-approx-80m%c2%b2-with-storage-area-of-approx-30m%c2%b2-in-the-base-plainpalais-820-821-1-17/</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1585,12 +1581,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-17 16:10:09</t>
+          <t>2026-03-17 21:42:39</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-03-17 19:08:46</t>
+          <t>2026-03-17 21:42:39</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1599,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1622,12 +1618,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-80m%c2%b2-avec-depot-denv-30m%c2%b2-au-sous-solarcade-of-approx-80m%c2%b2-with-storage-area-of-approx-30m%c2%b2-in-the-base-plainpalais-820-821-1-17/</t>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denviron-82-m%c2%b2-au-rez-de-chaussee82-m%c2%b2-arcade-on-ground-floor-plainpalais-9680-9681-1-13/</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1637,29 +1633,33 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-17 16:10:09</t>
+          <t>2026-03-17 21:42:39</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-03-17 19:08:46</t>
+          <t>2026-03-17 21:42:39</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rosset</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>pilet_renaud</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ACACIAS - CHF 374.-/m2 - Arcade d'environ 72m² Jonction-Plainpalais-Arve Rive, Les Acacias Loyer CHF 2’245.-</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Plainpalais</t>
+          <t>Rive</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1674,27 +1674,27 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denviron-82-m%c2%b2-au-rez-de-chaussee82-m%c2%b2-arcade-on-ground-floor-plainpalais-9680-9681-1-13/</t>
+          <t>https://www.pilet-renaud.ch/fr/a-louer//acacias-chf-374-m2-arcade-denviron-72m--8598</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-17 16:10:09</t>
+          <t>2026-03-17 21:42:39</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-03-17 19:08:46</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17 19:08:46</t>
+          <t>2026-03-17 21:42:39</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17 19:08:46</t>
+          <t>2026-03-17 21:42:39</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-17 21:42:39</t>
+          <t>2026-03-18 02:35:31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-17 21:42:39</t>
+          <t>2026-03-18 02:35:31</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17 21:42:39</t>
+          <t>2026-03-18 02:35:31</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-17 21:42:39</t>
+          <t>2026-03-18 02:35:31</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-17 21:42:39</t>
+          <t>2026-03-18 02:35:31</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-17 21:42:39</t>
+          <t>2026-03-18 02:35:31</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17 21:42:39</t>
+          <t>2026-03-18 02:35:31</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17 21:42:39</t>
+          <t>2026-03-18 02:35:31</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18 02:35:31</t>
+          <t>2026-03-18 05:01:14</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18 02:35:31</t>
+          <t>2026-03-18 05:01:14</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18 02:35:31</t>
+          <t>2026-03-18 05:01:14</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18 02:35:31</t>
+          <t>2026-03-18 05:01:14</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18 02:35:31</t>
+          <t>2026-03-18 05:01:14</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18 02:35:31</t>
+          <t>2026-03-18 05:01:14</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18 02:35:31</t>
+          <t>2026-03-18 05:01:14</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18 02:35:31</t>
+          <t>2026-03-18 05:01:14</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18 05:01:14</t>
+          <t>2026-03-18 07:07:36</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18 05:01:14</t>
+          <t>2026-03-18 07:07:36</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18 05:01:14</t>
+          <t>2026-03-18 07:07:36</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18 05:01:14</t>
+          <t>2026-03-18 07:07:36</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18 05:01:14</t>
+          <t>2026-03-18 07:07:36</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18 05:01:14</t>
+          <t>2026-03-18 07:07:36</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18 05:01:14</t>
+          <t>2026-03-18 07:07:36</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18 05:01:14</t>
+          <t>2026-03-18 07:07:36</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18 07:07:36</t>
+          <t>2026-03-18 10:00:56</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18 07:07:36</t>
+          <t>2026-03-18 10:00:56</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18 07:07:36</t>
+          <t>2026-03-18 10:00:56</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18 07:07:36</t>
+          <t>2026-03-18 10:00:56</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18 07:07:36</t>
+          <t>2026-03-18 10:00:56</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18 07:07:36</t>
+          <t>2026-03-18 10:00:56</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18 07:07:36</t>
+          <t>2026-03-18 10:00:56</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18 07:07:36</t>
+          <t>2026-03-18 10:00:56</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18 10:00:56</t>
+          <t>2026-03-18 13:24:13</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18 10:00:56</t>
+          <t>2026-03-18 13:24:13</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18 10:00:56</t>
+          <t>2026-03-18 13:24:13</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18 10:00:56</t>
+          <t>2026-03-18 13:24:13</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18 10:00:56</t>
+          <t>2026-03-18 13:24:13</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18 10:00:56</t>
+          <t>2026-03-18 13:24:13</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18 10:00:56</t>
+          <t>2026-03-18 13:24:13</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18 10:00:56</t>
+          <t>2026-03-18 13:24:13</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18 13:24:13</t>
+          <t>2026-03-18 16:11:19</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18 13:24:13</t>
+          <t>2026-03-18 16:11:19</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18 13:24:13</t>
+          <t>2026-03-18 16:11:19</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18 13:24:13</t>
+          <t>2026-03-18 16:11:19</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18 13:24:13</t>
+          <t>2026-03-18 16:11:19</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18 13:24:13</t>
+          <t>2026-03-18 16:11:19</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18 13:24:13</t>
+          <t>2026-03-18 16:11:19</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18 13:24:13</t>
+          <t>2026-03-18 16:11:19</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18 16:11:19</t>
+          <t>2026-03-18 19:07:22</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18 16:11:19</t>
+          <t>2026-03-18 19:07:22</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18 16:11:19</t>
+          <t>2026-03-18 19:07:22</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18 16:11:19</t>
+          <t>2026-03-18 19:07:22</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18 16:11:19</t>
+          <t>2026-03-18 19:07:22</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18 16:11:19</t>
+          <t>2026-03-18 19:07:22</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18 16:11:19</t>
+          <t>2026-03-18 19:07:22</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18 16:11:19</t>
+          <t>2026-03-18 19:07:22</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18 19:07:22</t>
+          <t>2026-03-18 21:39:37</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18 19:07:22</t>
+          <t>2026-03-18 21:39:37</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18 19:07:22</t>
+          <t>2026-03-18 21:39:37</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18 19:07:22</t>
+          <t>2026-03-18 21:39:37</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18 19:07:22</t>
+          <t>2026-03-18 21:39:37</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18 19:07:22</t>
+          <t>2026-03-18 21:39:37</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18 19:07:22</t>
+          <t>2026-03-18 21:39:37</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18 19:07:22</t>
+          <t>2026-03-18 21:39:37</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18 21:39:37</t>
+          <t>2026-03-19 02:37:17</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18 21:39:37</t>
+          <t>2026-03-19 02:37:17</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18 21:39:37</t>
+          <t>2026-03-19 02:37:17</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18 21:39:37</t>
+          <t>2026-03-19 02:37:17</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18 21:39:37</t>
+          <t>2026-03-19 02:37:17</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18 21:39:37</t>
+          <t>2026-03-19 02:37:17</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18 21:39:37</t>
+          <t>2026-03-19 02:37:17</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18 21:39:37</t>
+          <t>2026-03-19 02:37:17</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19 02:37:17</t>
+          <t>2026-03-19 04:58:58</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19 02:37:17</t>
+          <t>2026-03-19 04:58:58</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19 02:37:17</t>
+          <t>2026-03-19 04:58:58</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19 02:37:17</t>
+          <t>2026-03-19 04:58:58</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19 02:37:17</t>
+          <t>2026-03-19 04:58:58</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-19 02:37:17</t>
+          <t>2026-03-19 04:58:58</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19 02:37:17</t>
+          <t>2026-03-19 04:58:58</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19 02:37:17</t>
+          <t>2026-03-19 04:58:58</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19 04:58:58</t>
+          <t>2026-03-19 07:04:36</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19 04:58:58</t>
+          <t>2026-03-19 07:04:36</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19 04:58:58</t>
+          <t>2026-03-19 07:04:36</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19 04:58:58</t>
+          <t>2026-03-19 07:04:36</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19 04:58:58</t>
+          <t>2026-03-19 07:04:36</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-19 04:58:58</t>
+          <t>2026-03-19 07:04:36</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19 04:58:58</t>
+          <t>2026-03-19 07:04:36</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19 04:58:58</t>
+          <t>2026-03-19 07:04:36</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19 07:04:36</t>
+          <t>2026-03-19 09:52:14</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19 07:04:36</t>
+          <t>2026-03-19 09:52:14</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19 07:04:36</t>
+          <t>2026-03-19 09:52:14</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19 07:04:36</t>
+          <t>2026-03-19 09:52:14</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19 07:04:36</t>
+          <t>2026-03-19 09:52:14</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-19 09:52:14</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19 07:04:36</t>
+          <t>2026-03-19 09:52:14</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19 07:04:36</t>
+          <t>2026-03-19 09:52:14</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19 09:52:14</t>
+          <t>2026-03-19 13:14:56</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19 09:52:14</t>
+          <t>2026-03-19 13:14:56</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19 09:52:14</t>
+          <t>2026-03-19 13:14:56</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19 09:52:14</t>
+          <t>2026-03-19 13:14:56</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19 09:52:14</t>
+          <t>2026-03-19 13:14:56</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19 09:52:14</t>
+          <t>2026-03-19 13:14:56</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19 09:52:14</t>
+          <t>2026-03-19 13:14:56</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19 13:14:56</t>
+          <t>2026-03-19 15:59:15</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19 13:14:56</t>
+          <t>2026-03-19 15:59:15</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19 13:14:56</t>
+          <t>2026-03-19 15:59:15</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19 13:14:56</t>
+          <t>2026-03-19 15:59:15</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19 13:14:56</t>
+          <t>2026-03-19 15:59:15</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19 13:14:56</t>
+          <t>2026-03-19 15:59:15</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19 13:14:56</t>
+          <t>2026-03-19 15:59:15</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19 15:59:15</t>
+          <t>2026-03-19 19:04:58</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19 15:59:15</t>
+          <t>2026-03-19 19:04:58</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19 15:59:15</t>
+          <t>2026-03-19 19:04:58</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19 15:59:15</t>
+          <t>2026-03-19 19:04:58</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19 15:59:15</t>
+          <t>2026-03-19 19:04:58</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19 15:59:15</t>
+          <t>2026-03-19 19:04:58</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19 15:59:15</t>
+          <t>2026-03-19 19:04:58</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19 19:04:58</t>
+          <t>2026-03-19 21:40:45</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19 19:04:58</t>
+          <t>2026-03-19 21:40:45</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19 19:04:58</t>
+          <t>2026-03-19 21:40:45</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19 19:04:58</t>
+          <t>2026-03-19 21:40:45</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19 19:04:58</t>
+          <t>2026-03-19 21:40:45</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19 19:04:58</t>
+          <t>2026-03-19 21:40:45</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19 19:04:58</t>
+          <t>2026-03-19 21:40:45</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19 21:40:45</t>
+          <t>2026-03-20 02:28:57</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19 21:40:45</t>
+          <t>2026-03-20 02:28:57</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19 21:40:45</t>
+          <t>2026-03-20 02:28:57</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19 21:40:45</t>
+          <t>2026-03-20 02:28:57</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19 21:40:45</t>
+          <t>2026-03-20 02:28:57</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19 21:40:45</t>
+          <t>2026-03-20 02:28:57</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19 21:40:45</t>
+          <t>2026-03-20 02:28:57</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20 02:28:57</t>
+          <t>2026-03-20 04:51:11</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20 02:28:57</t>
+          <t>2026-03-20 04:51:11</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20 02:28:57</t>
+          <t>2026-03-20 04:51:11</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20 02:28:57</t>
+          <t>2026-03-20 04:51:11</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20 02:28:57</t>
+          <t>2026-03-20 04:51:11</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20 02:28:57</t>
+          <t>2026-03-20 04:51:11</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20 02:28:57</t>
+          <t>2026-03-20 04:51:11</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20 04:51:11</t>
+          <t>2026-03-20 07:02:24</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20 04:51:11</t>
+          <t>2026-03-20 07:02:24</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20 04:51:11</t>
+          <t>2026-03-20 07:02:24</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20 04:51:11</t>
+          <t>2026-03-20 07:02:24</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20 04:51:11</t>
+          <t>2026-03-20 07:02:24</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20 04:51:11</t>
+          <t>2026-03-20 07:02:24</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20 04:51:11</t>
+          <t>2026-03-20 07:02:24</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20 07:02:24</t>
+          <t>2026-03-20 09:49:48</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20 07:02:24</t>
+          <t>2026-03-20 09:49:48</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20 07:02:24</t>
+          <t>2026-03-20 09:49:48</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20 07:02:24</t>
+          <t>2026-03-20 09:49:48</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20 07:02:24</t>
+          <t>2026-03-20 09:49:48</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20 07:02:24</t>
+          <t>2026-03-20 09:49:48</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20 07:02:24</t>
+          <t>2026-03-20 09:49:48</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20 09:49:48</t>
+          <t>2026-03-20 13:08:39</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20 09:49:48</t>
+          <t>2026-03-20 13:08:39</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20 09:49:48</t>
+          <t>2026-03-20 13:08:39</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20 09:49:48</t>
+          <t>2026-03-20 13:08:39</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20 09:49:48</t>
+          <t>2026-03-20 13:08:39</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20 09:49:48</t>
+          <t>2026-03-20 13:08:39</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20 09:49:48</t>
+          <t>2026-03-20 13:08:39</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20 13:08:39</t>
+          <t>2026-03-20 15:48:56</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20 13:08:39</t>
+          <t>2026-03-20 15:48:56</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20 13:08:39</t>
+          <t>2026-03-20 15:48:56</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20 13:08:39</t>
+          <t>2026-03-20 15:48:56</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20 13:08:39</t>
+          <t>2026-03-20 15:48:56</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20 13:08:39</t>
+          <t>2026-03-20 15:48:56</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20 13:08:39</t>
+          <t>2026-03-20 15:48:56</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20 15:48:56</t>
+          <t>2026-03-20 18:57:03</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20 15:48:56</t>
+          <t>2026-03-20 18:57:03</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20 15:48:56</t>
+          <t>2026-03-20 18:57:03</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20 15:48:56</t>
+          <t>2026-03-20 18:57:03</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20 15:48:56</t>
+          <t>2026-03-20 18:57:03</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20 15:48:56</t>
+          <t>2026-03-20 18:57:03</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20 15:48:56</t>
+          <t>2026-03-20 18:57:03</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20 18:57:03</t>
+          <t>2026-03-20 21:35:29</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20 18:57:03</t>
+          <t>2026-03-20 21:35:29</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20 18:57:03</t>
+          <t>2026-03-20 21:35:29</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20 18:57:03</t>
+          <t>2026-03-20 21:35:29</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20 18:57:03</t>
+          <t>2026-03-20 21:35:29</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20 18:57:03</t>
+          <t>2026-03-20 21:35:29</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20 18:57:03</t>
+          <t>2026-03-20 21:35:29</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20 21:35:29</t>
+          <t>2026-03-21 02:23:25</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20 21:35:29</t>
+          <t>2026-03-21 02:23:25</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20 21:35:29</t>
+          <t>2026-03-21 02:23:25</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20 21:35:29</t>
+          <t>2026-03-21 02:23:25</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20 21:35:29</t>
+          <t>2026-03-21 02:23:25</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20 21:35:29</t>
+          <t>2026-03-21 02:23:25</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20 21:35:29</t>
+          <t>2026-03-21 02:23:25</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21 02:23:25</t>
+          <t>2026-03-21 04:41:04</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21 02:23:25</t>
+          <t>2026-03-21 04:41:04</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21 02:23:25</t>
+          <t>2026-03-21 04:41:04</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21 02:23:25</t>
+          <t>2026-03-21 04:41:04</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21 02:23:25</t>
+          <t>2026-03-21 04:41:04</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21 02:23:25</t>
+          <t>2026-03-21 04:41:04</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21 02:23:25</t>
+          <t>2026-03-21 04:41:04</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21 04:41:04</t>
+          <t>2026-03-21 06:52:28</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21 04:41:04</t>
+          <t>2026-03-21 06:52:28</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21 04:41:04</t>
+          <t>2026-03-21 06:52:28</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21 04:41:04</t>
+          <t>2026-03-21 06:52:28</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21 04:41:04</t>
+          <t>2026-03-21 06:52:28</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21 04:41:04</t>
+          <t>2026-03-21 06:52:28</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21 04:41:04</t>
+          <t>2026-03-21 06:52:28</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21 06:52:28</t>
+          <t>2026-03-21 09:37:33</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21 06:52:28</t>
+          <t>2026-03-21 09:37:33</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21 06:52:28</t>
+          <t>2026-03-21 09:37:33</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21 06:52:28</t>
+          <t>2026-03-21 09:37:33</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21 06:52:28</t>
+          <t>2026-03-21 09:37:33</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21 06:52:28</t>
+          <t>2026-03-21 09:37:33</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21 06:52:28</t>
+          <t>2026-03-21 09:37:33</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21 09:37:33</t>
+          <t>2026-03-21 12:58:31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21 09:37:33</t>
+          <t>2026-03-21 12:58:31</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21 09:37:33</t>
+          <t>2026-03-21 12:58:31</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21 09:37:33</t>
+          <t>2026-03-21 12:58:31</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21 09:37:33</t>
+          <t>2026-03-21 12:58:31</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21 09:37:33</t>
+          <t>2026-03-21 12:58:31</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21 09:37:33</t>
+          <t>2026-03-21 12:58:31</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21 12:58:31</t>
+          <t>2026-03-21 15:30:54</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21 12:58:31</t>
+          <t>2026-03-21 15:30:54</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21 12:58:31</t>
+          <t>2026-03-21 15:30:54</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21 12:58:31</t>
+          <t>2026-03-21 15:30:54</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21 12:58:31</t>
+          <t>2026-03-21 15:30:54</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21 12:58:31</t>
+          <t>2026-03-21 15:30:54</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21 12:58:31</t>
+          <t>2026-03-21 15:30:54</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21 15:30:54</t>
+          <t>2026-03-21 18:42:12</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21 15:30:54</t>
+          <t>2026-03-21 18:42:12</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21 15:30:54</t>
+          <t>2026-03-21 18:42:12</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21 15:30:54</t>
+          <t>2026-03-21 18:42:12</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21 15:30:54</t>
+          <t>2026-03-21 18:42:12</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21 15:30:54</t>
+          <t>2026-03-21 18:42:12</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21 15:30:54</t>
+          <t>2026-03-21 18:42:12</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21 18:42:12</t>
+          <t>2026-03-21 21:30:44</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21 18:42:12</t>
+          <t>2026-03-21 21:30:44</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21 18:42:12</t>
+          <t>2026-03-21 21:30:44</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21 18:42:12</t>
+          <t>2026-03-21 21:30:44</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21 18:42:12</t>
+          <t>2026-03-21 21:30:44</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21 18:42:12</t>
+          <t>2026-03-21 21:30:44</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21 18:42:12</t>
+          <t>2026-03-21 21:30:44</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21 21:30:44</t>
+          <t>2026-03-22 02:37:40</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21 21:30:44</t>
+          <t>2026-03-22 02:37:40</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21 21:30:44</t>
+          <t>2026-03-22 02:37:40</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21 21:30:44</t>
+          <t>2026-03-22 02:37:40</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21 21:30:44</t>
+          <t>2026-03-22 02:37:40</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21 21:30:44</t>
+          <t>2026-03-22 02:37:40</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21 21:30:44</t>
+          <t>2026-03-22 02:37:40</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22 02:37:40</t>
+          <t>2026-03-22 04:56:35</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22 02:37:40</t>
+          <t>2026-03-22 04:56:35</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22 02:37:40</t>
+          <t>2026-03-22 04:56:35</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22 02:37:40</t>
+          <t>2026-03-22 04:56:35</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22 02:37:40</t>
+          <t>2026-03-22 04:56:35</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22 02:37:40</t>
+          <t>2026-03-22 04:56:35</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22 02:37:40</t>
+          <t>2026-03-22 04:56:35</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22 04:56:35</t>
+          <t>2026-03-22 06:58:14</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22 04:56:35</t>
+          <t>2026-03-22 06:58:14</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22 04:56:35</t>
+          <t>2026-03-22 06:58:14</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22 04:56:35</t>
+          <t>2026-03-22 06:58:14</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22 04:56:35</t>
+          <t>2026-03-22 06:58:14</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22 04:56:35</t>
+          <t>2026-03-22 06:58:14</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22 04:56:35</t>
+          <t>2026-03-22 06:58:14</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22 06:58:14</t>
+          <t>2026-03-22 09:38:16</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22 06:58:14</t>
+          <t>2026-03-22 09:38:16</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22 06:58:14</t>
+          <t>2026-03-22 09:38:16</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22 06:58:14</t>
+          <t>2026-03-22 09:38:16</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22 06:58:14</t>
+          <t>2026-03-22 09:38:16</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22 06:58:14</t>
+          <t>2026-03-22 09:38:16</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22 06:58:14</t>
+          <t>2026-03-22 09:38:16</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22 09:38:16</t>
+          <t>2026-03-22 13:00:41</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22 09:38:16</t>
+          <t>2026-03-22 13:00:41</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22 09:38:16</t>
+          <t>2026-03-22 13:00:41</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22 09:38:16</t>
+          <t>2026-03-22 13:00:41</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22 09:38:16</t>
+          <t>2026-03-22 13:00:41</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22 09:38:16</t>
+          <t>2026-03-22 13:00:41</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22 09:38:16</t>
+          <t>2026-03-22 13:00:41</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22 13:00:41</t>
+          <t>2026-03-22 15:31:20</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22 13:00:41</t>
+          <t>2026-03-22 15:31:20</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22 13:00:41</t>
+          <t>2026-03-22 15:31:20</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22 13:00:41</t>
+          <t>2026-03-22 15:31:20</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22 13:00:41</t>
+          <t>2026-03-22 15:31:20</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22 13:00:41</t>
+          <t>2026-03-22 15:31:20</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22 13:00:41</t>
+          <t>2026-03-22 15:31:20</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22 15:31:20</t>
+          <t>2026-03-22 18:43:28</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22 15:31:20</t>
+          <t>2026-03-22 18:43:28</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22 15:31:20</t>
+          <t>2026-03-22 18:43:28</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22 15:31:20</t>
+          <t>2026-03-22 18:43:28</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22 15:31:20</t>
+          <t>2026-03-22 18:43:28</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22 15:31:20</t>
+          <t>2026-03-22 18:43:28</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22 15:31:20</t>
+          <t>2026-03-22 18:43:28</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22 18:43:28</t>
+          <t>2026-03-22 21:31:46</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22 18:43:28</t>
+          <t>2026-03-22 21:31:46</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22 18:43:28</t>
+          <t>2026-03-22 21:31:46</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22 18:43:28</t>
+          <t>2026-03-22 21:31:46</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22 18:43:28</t>
+          <t>2026-03-22 21:31:46</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22 18:43:28</t>
+          <t>2026-03-22 21:31:46</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22 18:43:28</t>
+          <t>2026-03-22 21:31:46</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22 21:31:46</t>
+          <t>2026-03-23 02:38:21</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22 21:31:46</t>
+          <t>2026-03-23 02:38:21</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22 21:31:46</t>
+          <t>2026-03-23 02:38:21</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22 21:31:46</t>
+          <t>2026-03-23 02:38:21</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22 21:31:46</t>
+          <t>2026-03-23 02:38:21</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22 21:31:46</t>
+          <t>2026-03-23 02:38:21</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22 21:31:46</t>
+          <t>2026-03-23 02:38:21</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-23 02:38:21</t>
+          <t>2026-03-23 05:07:45</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-23 02:38:21</t>
+          <t>2026-03-23 05:07:45</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-23 02:38:21</t>
+          <t>2026-03-23 05:07:45</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-23 02:38:21</t>
+          <t>2026-03-23 05:07:45</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-23 02:38:21</t>
+          <t>2026-03-23 05:07:45</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-23 02:38:21</t>
+          <t>2026-03-23 05:07:45</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-23 02:38:21</t>
+          <t>2026-03-23 05:07:45</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-23 05:07:45</t>
+          <t>2026-03-23 07:17:41</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-23 05:07:45</t>
+          <t>2026-03-23 07:17:41</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-23 05:07:45</t>
+          <t>2026-03-23 07:17:41</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-23 05:07:45</t>
+          <t>2026-03-23 07:17:41</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-23 05:07:45</t>
+          <t>2026-03-23 07:17:41</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-23 05:07:45</t>
+          <t>2026-03-23 07:17:41</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-23 05:07:45</t>
+          <t>2026-03-23 07:17:41</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-23 07:17:41</t>
+          <t>2026-03-23 10:06:51</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-23 07:17:41</t>
+          <t>2026-03-23 10:06:51</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-23 07:17:41</t>
+          <t>2026-03-23 10:06:51</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-23 07:17:41</t>
+          <t>2026-03-23 10:06:51</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-23 07:17:41</t>
+          <t>2026-03-23 10:06:51</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-23 07:17:41</t>
+          <t>2026-03-23 10:06:51</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-23 07:17:41</t>
+          <t>2026-03-23 10:06:51</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-23 10:06:51</t>
+          <t>2026-03-23 13:18:29</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-23 10:06:51</t>
+          <t>2026-03-23 13:18:29</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-23 10:06:51</t>
+          <t>2026-03-23 13:18:29</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-23 10:06:51</t>
+          <t>2026-03-23 13:18:29</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-23 10:06:51</t>
+          <t>2026-03-23 13:18:29</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-23 13:18:29</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-03-16 23:49:00</t>
+          <t>2026-03-23 13:18:29</t>
         </is>
       </c>
     </row>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-23 13:18:29</t>
+          <t>2026-03-23 16:03:41</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-23 13:18:29</t>
+          <t>2026-03-23 16:03:41</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-23 13:18:29</t>
+          <t>2026-03-23 16:03:41</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-23 13:18:29</t>
+          <t>2026-03-23 16:03:41</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-23 13:18:29</t>
+          <t>2026-03-23 16:03:41</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-23 10:06:51</t>
+          <t>2026-03-23 16:03:41</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-03-23 13:18:29</t>
+          <t>2026-03-23 16:03:41</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-23 10:06:51</t>
+          <t>2026-03-23 16:03:41</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-03-23 13:18:29</t>
+          <t>2026-03-23 16:03:41</t>
         </is>
       </c>
     </row>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-23 16:03:41</t>
+          <t>2026-03-23 19:01:19</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-23 16:03:41</t>
+          <t>2026-03-23 19:01:19</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-23 16:03:41</t>
+          <t>2026-03-23 19:01:19</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-23 16:03:41</t>
+          <t>2026-03-23 19:01:19</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-23 16:03:41</t>
+          <t>2026-03-23 19:01:19</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-23 16:03:41</t>
+          <t>2026-03-23 19:01:19</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-23 16:03:41</t>
+          <t>2026-03-23 19:01:19</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-23 19:01:19</t>
+          <t>2026-03-23 21:41:37</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-23 19:01:19</t>
+          <t>2026-03-23 21:41:37</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-23 19:01:19</t>
+          <t>2026-03-23 21:41:37</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-23 19:01:19</t>
+          <t>2026-03-23 21:41:37</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-23 19:01:19</t>
+          <t>2026-03-23 21:41:37</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-23 19:01:19</t>
+          <t>2026-03-23 21:41:37</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-23 19:01:19</t>
+          <t>2026-03-23 21:41:37</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-23 21:41:37</t>
+          <t>2026-03-24 02:29:43</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-23 21:41:37</t>
+          <t>2026-03-24 02:29:43</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-23 21:41:37</t>
+          <t>2026-03-24 02:29:43</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-23 21:41:37</t>
+          <t>2026-03-24 02:29:43</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-23 21:41:37</t>
+          <t>2026-03-24 02:29:43</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-23 21:41:37</t>
+          <t>2026-03-24 02:29:43</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-23 21:41:37</t>
+          <t>2026-03-24 02:29:43</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-24 02:29:43</t>
+          <t>2026-03-24 04:58:07</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-24 02:29:43</t>
+          <t>2026-03-24 04:58:07</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-24 02:29:43</t>
+          <t>2026-03-24 04:58:07</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-24 02:29:43</t>
+          <t>2026-03-24 04:58:07</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-24 02:29:43</t>
+          <t>2026-03-24 04:58:07</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-24 02:29:43</t>
+          <t>2026-03-24 04:58:07</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-24 02:29:43</t>
+          <t>2026-03-24 04:58:07</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-24 04:58:07</t>
+          <t>2026-03-24 07:10:52</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-24 04:58:07</t>
+          <t>2026-03-24 07:10:52</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-24 04:58:07</t>
+          <t>2026-03-24 07:10:52</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-24 04:58:07</t>
+          <t>2026-03-24 07:10:52</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-24 04:58:07</t>
+          <t>2026-03-24 07:10:52</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-24 04:58:07</t>
+          <t>2026-03-24 07:10:52</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-24 04:58:07</t>
+          <t>2026-03-24 07:10:52</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-24 07:10:52</t>
+          <t>2026-03-24 10:00:08</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-24 07:10:52</t>
+          <t>2026-03-24 10:00:08</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-24 07:10:52</t>
+          <t>2026-03-24 10:00:08</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-24 07:10:52</t>
+          <t>2026-03-24 10:00:08</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-24 07:10:52</t>
+          <t>2026-03-24 10:00:08</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-24 07:10:52</t>
+          <t>2026-03-24 10:00:08</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-24 07:10:52</t>
+          <t>2026-03-24 10:00:08</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-24 10:00:08</t>
+          <t>2026-03-24 13:21:24</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-24 10:00:08</t>
+          <t>2026-03-24 13:21:24</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-24 10:00:08</t>
+          <t>2026-03-24 13:21:24</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-24 10:00:08</t>
+          <t>2026-03-24 13:21:24</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-24 10:00:08</t>
+          <t>2026-03-24 13:21:24</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-24 10:00:08</t>
+          <t>2026-03-24 13:21:24</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-24 10:00:08</t>
+          <t>2026-03-24 13:21:24</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-24 13:21:24</t>
+          <t>2026-03-24 16:10:39</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-24 13:21:24</t>
+          <t>2026-03-24 16:10:39</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-24 13:21:24</t>
+          <t>2026-03-24 16:10:39</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-24 13:21:24</t>
+          <t>2026-03-24 16:10:39</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-24 13:21:24</t>
+          <t>2026-03-24 16:10:39</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-24 13:21:24</t>
+          <t>2026-03-24 16:10:39</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-24 13:21:24</t>
+          <t>2026-03-24 16:10:39</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-24 16:10:39</t>
+          <t>2026-03-24 19:09:52</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-24 16:10:39</t>
+          <t>2026-03-24 19:09:52</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-24 16:10:39</t>
+          <t>2026-03-24 19:09:52</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-24 16:10:39</t>
+          <t>2026-03-24 19:09:52</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-24 16:10:39</t>
+          <t>2026-03-24 19:09:52</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-24 16:10:39</t>
+          <t>2026-03-24 19:09:52</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-24 16:10:39</t>
+          <t>2026-03-24 19:09:52</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-24 19:09:52</t>
+          <t>2026-03-24 21:42:24</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-24 19:09:52</t>
+          <t>2026-03-24 21:42:24</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-24 19:09:52</t>
+          <t>2026-03-24 21:42:24</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-24 19:09:52</t>
+          <t>2026-03-24 21:42:24</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-24 19:09:52</t>
+          <t>2026-03-24 21:42:24</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-24 19:09:52</t>
+          <t>2026-03-24 21:42:24</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-24 19:09:52</t>
+          <t>2026-03-24 21:42:24</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-24 21:42:24</t>
+          <t>2026-03-25 02:34:42</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-24 21:42:24</t>
+          <t>2026-03-25 02:34:42</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-24 21:42:24</t>
+          <t>2026-03-25 02:34:42</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-24 21:42:24</t>
+          <t>2026-03-25 02:34:42</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-24 21:42:24</t>
+          <t>2026-03-25 02:34:42</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-24 21:42:24</t>
+          <t>2026-03-25 02:34:42</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-24 21:42:24</t>
+          <t>2026-03-25 02:34:42</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-25 02:34:42</t>
+          <t>2026-03-25 04:58:38</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-25 02:34:42</t>
+          <t>2026-03-25 04:58:38</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-25 02:34:42</t>
+          <t>2026-03-25 04:58:38</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-25 02:34:42</t>
+          <t>2026-03-25 04:58:38</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-25 02:34:42</t>
+          <t>2026-03-25 04:58:38</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-25 02:34:42</t>
+          <t>2026-03-25 04:58:38</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-25 02:34:42</t>
+          <t>2026-03-25 04:58:38</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-25 04:58:38</t>
+          <t>2026-03-25 07:08:45</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-25 04:58:38</t>
+          <t>2026-03-25 07:08:45</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-25 04:58:38</t>
+          <t>2026-03-25 07:08:45</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-25 04:58:38</t>
+          <t>2026-03-25 07:08:45</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-25 04:58:38</t>
+          <t>2026-03-25 07:08:45</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-25 04:58:38</t>
+          <t>2026-03-25 07:08:45</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-25 04:58:38</t>
+          <t>2026-03-25 07:08:45</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-25 07:08:45</t>
+          <t>2026-03-25 09:58:58</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-25 07:08:45</t>
+          <t>2026-03-25 09:58:58</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-25 07:08:45</t>
+          <t>2026-03-25 09:58:58</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-25 07:08:45</t>
+          <t>2026-03-25 09:58:58</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-25 07:08:45</t>
+          <t>2026-03-25 09:58:58</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-25 07:08:45</t>
+          <t>2026-03-25 09:58:58</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-25 07:08:45</t>
+          <t>2026-03-25 09:58:58</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-25 09:58:58</t>
+          <t>2026-03-25 13:20:31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-25 09:58:58</t>
+          <t>2026-03-25 13:20:31</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-25 09:58:58</t>
+          <t>2026-03-25 13:20:31</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-25 09:58:58</t>
+          <t>2026-03-25 13:20:31</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-25 09:58:58</t>
+          <t>2026-03-25 13:20:31</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-25 09:58:58</t>
+          <t>2026-03-25 13:20:31</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-25 09:58:58</t>
+          <t>2026-03-25 13:20:31</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-25 13:20:31</t>
+          <t>2026-03-25 16:14:51</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-25 13:20:31</t>
+          <t>2026-03-25 16:14:51</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-25 13:20:31</t>
+          <t>2026-03-25 16:14:51</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-25 13:20:31</t>
+          <t>2026-03-25 16:14:51</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-25 13:20:31</t>
+          <t>2026-03-25 16:14:51</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-25 13:20:31</t>
+          <t>2026-03-25 16:14:51</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-25 13:20:31</t>
+          <t>2026-03-25 16:14:51</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-25 16:14:51</t>
+          <t>2026-03-25 19:01:54</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-25 16:14:51</t>
+          <t>2026-03-25 19:01:54</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-25 16:14:51</t>
+          <t>2026-03-25 19:01:54</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-25 16:14:51</t>
+          <t>2026-03-25 19:01:54</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-25 16:14:51</t>
+          <t>2026-03-25 19:01:54</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-25 16:14:51</t>
+          <t>2026-03-25 19:01:54</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-25 16:14:51</t>
+          <t>2026-03-25 19:01:54</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-25 19:01:54</t>
+          <t>2026-03-25 21:44:25</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-25 19:01:54</t>
+          <t>2026-03-25 21:44:25</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-25 19:01:54</t>
+          <t>2026-03-25 21:44:25</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-25 19:01:54</t>
+          <t>2026-03-25 21:44:25</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-25 19:01:54</t>
+          <t>2026-03-25 21:44:25</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-25 19:01:54</t>
+          <t>2026-03-25 21:44:25</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-25 19:01:54</t>
+          <t>2026-03-25 21:44:25</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-25 21:44:25</t>
+          <t>2026-03-26 02:41:59</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-25 21:44:25</t>
+          <t>2026-03-26 02:41:59</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-25 21:44:25</t>
+          <t>2026-03-26 02:41:59</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-25 21:44:25</t>
+          <t>2026-03-26 02:41:59</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-25 21:44:25</t>
+          <t>2026-03-26 02:41:59</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-25 21:44:25</t>
+          <t>2026-03-26 02:41:59</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-25 21:44:25</t>
+          <t>2026-03-26 02:41:59</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-26 02:41:59</t>
+          <t>2026-03-26 05:11:17</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-26 02:41:59</t>
+          <t>2026-03-26 05:11:17</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-26 02:41:59</t>
+          <t>2026-03-26 05:11:17</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-26 02:41:59</t>
+          <t>2026-03-26 05:11:17</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-26 02:41:59</t>
+          <t>2026-03-26 05:11:17</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-26 02:41:59</t>
+          <t>2026-03-26 05:11:17</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-26 02:41:59</t>
+          <t>2026-03-26 05:11:17</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-26 05:11:17</t>
+          <t>2026-03-26 07:16:04</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-26 05:11:17</t>
+          <t>2026-03-26 07:16:04</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-26 05:11:17</t>
+          <t>2026-03-26 07:16:04</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-26 05:11:17</t>
+          <t>2026-03-26 07:16:04</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-26 05:11:17</t>
+          <t>2026-03-26 07:16:04</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-26 05:11:17</t>
+          <t>2026-03-26 07:16:04</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-26 05:11:17</t>
+          <t>2026-03-26 07:16:04</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-26 07:16:04</t>
+          <t>2026-03-26 08:41:35</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-26 07:16:04</t>
+          <t>2026-03-26 08:41:35</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-26 07:16:04</t>
+          <t>2026-03-26 08:41:35</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-26 07:16:04</t>
+          <t>2026-03-26 08:41:35</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-26 07:16:04</t>
+          <t>2026-03-26 08:41:35</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-03-23 16:03:41</t>
+          <t>2026-03-26 08:41:35</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-03-23 16:03:41</t>
+          <t>2026-03-26 08:41:35</t>
         </is>
       </c>
     </row>

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-26 08:41:35</t>
+          <t>2026-03-26 10:04:42</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-26 08:41:35</t>
+          <t>2026-03-26 10:04:42</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-26 08:41:35</t>
+          <t>2026-03-26 10:04:42</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-26 08:41:35</t>
+          <t>2026-03-26 10:04:42</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-26 08:41:35</t>
+          <t>2026-03-26 10:04:42</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">

--- a/data/listings.xlsx
+++ b/data/listings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,60 +441,50 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>price_chf_month</t>
+          <t>surface_m2</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>surface_m2</t>
+          <t>district</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>possible_changing_room</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>location_text</t>
+          <t>score</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>possible_changing_room</t>
+          <t>matches</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>status</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>matches</t>
+          <t>url</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>first_seen_at</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>last_seen_at</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>first_seen_at</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>last_seen_at</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>last_changed_at</t>
         </is>
@@ -512,51 +502,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>646</v>
-      </c>
-      <c r="D2" t="n">
         <v>263</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Rive</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>il y a 2 mois Classicus Real Estate SA 263 m² • Bureau Rue Eugène- Marziano 23, 1227 Les Acacias Agencement rare et complet 9 bureaux privés disponibles Places de parking à louer CHF 8’646 CHF 394 m² / year Classicus Real Estate SA Bureau à louer Rue Eugène- Marziano 23, 1227 Les Acacias Grande surface de bureaux au 2ème étage - 263 m² - Genève Plainpalais 263 m² • Bureau Agencement rare et complet 9 bureaux privés disponibles Places de parking à louer CHF 8’646 CHF 394 m² / year</t>
-        </is>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>85</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
-        <v>85</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/23-rue-eugene-marziano-1227-les-acacias-MXG4-7ZER</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/23-rue-eugene-marziano-1227-les-acacias-MXG4-7ZER</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -574,51 +556,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>288</v>
-      </c>
-      <c r="D3" t="n">
         <v>241</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Eaux-Vives</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 241 m² • Bureau Rue Des Eaux-Vives 94, 1207 Genève Espace lumineux et personnalisable Immeuble certifié Minergie Emplacement privilégié près du lac CHF 9’288 CHF 462 m² / year Naef Immobilier – Location Bureau à louer Rue Des Eaux-Vives 94, 1207 Genève Eaux-Vives : bureaux d'env 241m2 à louer 241 m² • Bureau Espace lumineux et personnalisable Immeuble certifié Minergie Emplacement privilégié près du lac CHF 9’288 CHF 462 m² / year</t>
-        </is>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>85</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
-        <v>85</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/94-rue-des-eaux-vives-1207-geneve-XEG4-2ZZX</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/94-rue-des-eaux-vives-1207-geneve-XEG4-2ZZX</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-03-16 13:22:39</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-03-16 16:10:21</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
         <is>
           <t>2026-03-16 19:09:59</t>
         </is>
@@ -636,47 +610,39 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>387</v>
-      </c>
-      <c r="D4" t="n">
         <v>244</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Aucune photo il y a 28 jours Zimmermann Immobilier 244 m² • Bureau Avenue Blanc, 1202 Genève Superficie de 244 m² Proche des organisations internationales Cuisine entièrement équipée CHF 7’387 CHF 363 m² / year Zimmermann Immobilier Bureau à louer Avenue Blanc, 1202 Genève Jolie arcade dans le quartier de Sécheron 244 m² • Bureau Superficie de 244 m² Proche des organisations internationales Cuisine entièrement équipée CHF 7’387 CHF 363 m² / year</t>
-        </is>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>80</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>80</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/avenue-blanc-1202-geneve-JDXL-OVQ4</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/avenue-blanc-1202-geneve-JDXL-OVQ4</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -694,47 +660,39 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>253</v>
-      </c>
-      <c r="D5" t="n">
         <v>352</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>il y a 1 mois Naef Immobilier – Location 352 m² • Arcade Rue De Richemont 10, 1202 Genève Emplacement idéal près de la gare Options d'aménagement flexibles Deux niveaux plus sous-sol CHF 12’253 CHF 418 m² / year Naef Immobilier – Location Arcade à louer Rue De Richemont 10, 1202 Genève Grande arcade au cur des Pâquis 352 m² • Arcade Emplacement idéal près de la gare Options d'aménagement flexibles Deux niveaux plus sous-sol CHF 12’253 CHF 418 m² / year</t>
-        </is>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>80</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>80</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/10-rue-de-richemont-1202-geneve-NAG4-74X4</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/10-rue-de-richemont-1202-geneve-NAG4-74X4</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -752,47 +710,39 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>470</v>
-      </c>
-      <c r="D6" t="n">
         <v>235</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>il y a 4 mois NESSELL Real Estate SA 5 pièces • 235 m² • Magasin 1205 Genève Idéal pour le yoga et la danse Lumière naturelle abondante Emplacement privilégié près des commerces CHF 7’470 CHF 381 m² / year NESSELL Real Estate SA Magasin à louer 1205 Genève Arcade spacieuse – idéale pour des activités sportives ou de bien-être 5 pièces • 235 m² • Magasin Idéal pour le yoga et la danse Lumière naturelle abondante Emplacement privilégié près des commerces CHF 7’470 CHF 381 m² / year</t>
-        </is>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>80</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>80</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/1205-geneve-4E56-OO2M</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1205-geneve-4E56-OO2M</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -810,51 +760,43 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>320</v>
-      </c>
-      <c r="D7" t="n">
         <v>130</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Plainpalais</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>il y a 2 mois Classicus Real Estate SA 130 m² • Bureau Rue Eugène- Marziano 23, 1227 Les Acacias Espace de travail calme Salle de réunion collaborative Places de parking extérieures CHF 4’320 CHF 399 m² / year Classicus Real Estate SA Bureau à louer Rue Eugène- Marziano 23, 1227 Les Acacias Bureaux professionnels rationnels au 2ème étage - Genève Plainpalais 130 m² • Bureau Espace de travail calme Salle de réunion collaborative Places de parking extérieures CHF 4’320 CHF 399 m² / year</t>
-        </is>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>75</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
-        <v>75</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/23-rue-eugene-marziano-1227-les-acacias-MXG4-7NR5</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/23-rue-eugene-marziano-1227-les-acacias-MXG4-7NR5</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -867,48 +809,46 @@
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="n">
+      <c r="C8" t="n">
         <v>253</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Plainpalais</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>70</v>
+      </c>
       <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>70</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denviron-253m%c2%b2-avec-rez-inferieur-denv-101m%c2%b2arcade-of-approx-253m%c2%b2-with-lower-ground-floor-of-approx-101m%c2%b2-plainpalais-carl-vogt-6640-6641-1-11/</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denviron-253m%c2%b2-avec-rez-inferieur-denv-101m%c2%b2arcade-of-approx-253m%c2%b2-with-lower-ground-floor-of-approx-101m%c2%b2-plainpalais-carl-vogt-6640-6641-1-11/</t>
+          <t>2026-03-26 10:04:42</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-03-26 10:04:42</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-03-17 21:42:39</t>
+          <t>2026-04-24 21:53:00</t>
         </is>
       </c>
     </row>
@@ -919,48 +859,46 @@
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="n">
+      <c r="C9" t="n">
         <v>388</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Eaux-Vives</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>70</v>
+      </c>
       <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>70</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denviron-388-m%c2%b2-dont-179-m%c2%b2-au-sous-solarcade-of-approx-388-m%c2%b2-179-m%c2%b2-of-which-in-the-basement-eaux-vives-1580-1581-2-13/</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denviron-388-m%c2%b2-dont-179-m%c2%b2-au-sous-solarcade-of-approx-388-m%c2%b2-179-m%c2%b2-of-which-in-the-basement-eaux-vives-1580-1581-2-13/</t>
+          <t>2026-03-26 10:04:42</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2026-03-26 10:04:42</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2026-03-17 21:42:39</t>
+          <t>2026-04-24 21:53:00</t>
         </is>
       </c>
     </row>
@@ -976,47 +914,39 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>460</v>
-      </c>
-      <c r="D10" t="n">
         <v>120</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>il y a 3 mois Naef Immobilier – Location 1 pièce • 120 m² • Arcade Rue Arnold- Winkelried 6, 1201 Genève Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year Naef Immobilier – Location Arcade à louer Rue Arnold- Winkelried 6, 1201 Genève Bergues - Arcade hypercentre 120m2 + 50m2 sous sol 1 pièce • 120 m² • Arcade Rénovation pour label Minergie Emplacement privilégié près des hôtels 120 m² plus 50 m² en sous-sol CHF 12’460 CHF 1’246 m² / year</t>
-        </is>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>70</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>70</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/6-rue-arnold-winkelried-1201-geneve-4E56-OQNE</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/6-rue-arnold-winkelried-1201-geneve-4E56-OQNE</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -1034,47 +964,39 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>362</v>
-      </c>
-      <c r="D11" t="n">
         <v>206</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>il y a 1 mois Naef Immobilier – Location 206 m² • Bureau Rue Rousseau 38, 1201 Genève Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year Naef Immobilier – Location Bureau à louer Rue Rousseau 38, 1201 Genève Bureau 206m2 à louer  Genève Centre, proche de la gare Cornavin 206 m² • Bureau Espace ouvert lumineux Salles de réunion équipées Service de conciergerie sur place CHF 11’362 CHF 662 m² / year</t>
-        </is>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>65</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="n">
-        <v>65</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/38-rue-rousseau-1201-geneve-QN34-7LBG</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/38-rue-rousseau-1201-geneve-QN34-7LBG</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -1092,47 +1014,39 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>947</v>
-      </c>
-      <c r="D12" t="n">
         <v>656</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 656 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 656 m2 - Surface high techn et industrielle au Cur de Genève 656 m² • Commercial Emplacement stratégique à Genève Espaces modulables flexibles Accès logistique direct CHF 16’947 CHF 310 m² / year</t>
-        </is>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>65</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="n">
-        <v>65</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-95R9-E66W</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-95R9-E66W</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -1150,47 +1064,39 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>688</v>
-      </c>
-      <c r="D13" t="n">
         <v>438</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 438 m² • Bureau Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year Naef Immobilier – Location Bureau à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 438m2 - Bureaux 438 m² • Bureau Emplacement stratégique à Genève Agencements de bureaux flexibles Accès direct aux transports CHF 13’688 CHF 375 m² / year</t>
-        </is>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>65</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="n">
-        <v>65</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-XEG4-2OOX</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-XEG4-2OOX</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -1208,47 +1114,39 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>865</v>
-      </c>
-      <c r="D14" t="n">
         <v>3272</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 3272 m² • Commercial Rue De Lyon 114, 1203 Genève Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year Naef Immobilier – Location Commercial à louer Rue De Lyon 114, 1203 Genève À LOUER  Quartet - 3272 m2 - Locaux Tertiaires et Secondaires au Cur de Genève 3272 m² • Commercial Emplacement stratégique à Genève Espaces flexibles pour divers usages Accès direct aux transports publics CHF 85’865 CHF 315 m² / year</t>
-        </is>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>65</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="n">
-        <v>65</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-LDX9-PVV2</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/114-rue-de-lyon-1203-geneve-LDX9-PVV2</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -1266,47 +1164,39 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>222</v>
-      </c>
-      <c r="D15" t="n">
         <v>258</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 258 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de Lausanne - Bureaux de 258 m² 258 m² • Bureau Emplacement stratégique près de l'ONU Aménagement de bureaux flexible Parking disponible sur place CHF 13’222 CHF 615 m² / year</t>
-        </is>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>65</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="n">
-        <v>65</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-ZZ74-D5V3</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-ZZ74-D5V3</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -1324,47 +1214,39 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>522</v>
-      </c>
-      <c r="D16" t="n">
         <v>316</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 316 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureaux de 316 m² au 3ème étage 316 m² • Bureau Emplacement privilégié près de Cornavin Bâtiment historique du XVIIIe siècle Agencements de bureaux flexibles CHF 16’522 CHF 627 m² / year</t>
-        </is>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>65</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="n">
-        <v>65</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-VBG4-7QXW</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-VBG4-7QXW</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -1382,47 +1264,39 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>637</v>
-      </c>
-      <c r="D17" t="n">
         <v>266</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 266 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureau de 266m² aux derniers étages 266 m² • Bureau Emplacement privilégié près de Cornavin Bureaux lumineux avec caractéristiques modernes Espace flexible pour divers usages CHF 9’637 CHF 435 m² / year</t>
-        </is>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>65</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="n">
-        <v>65</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-23ZJ-WQ7B</t>
+        </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-23ZJ-WQ7B</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -1440,47 +1314,39 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>276</v>
-      </c>
-      <c r="D18" t="n">
         <v>162</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 162 m² • Bureau Rue De Chantepoulet 25, 1201 Genève Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year Naef Immobilier – Location Bureau à louer Rue De Chantepoulet 25, 1201 Genève Chantepoulet - Bureau au 1er étage de 162 m² quartier dynamique 162 m² • Bureau Emplacement privilégié près de Cornavin Bureau lumineux de 162 m² Bâtiment historique du 18e siècle CHF 8’276 CHF 613 m² / year</t>
-        </is>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>55</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="n">
-        <v>55</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-LDX9-PZPW</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/25-rue-de-chantepoulet-1201-geneve-LDX9-PZPW</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -1493,48 +1359,46 @@
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="n">
+      <c r="C19" t="n">
         <v>90</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Rive</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>50</v>
+      </c>
       <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>50</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-90-m%c2%b2-au-rez-de-chausseearcade-of-approx-90-m%c2%b2-on-first-floor-rive-geneve-centre-1270-1271-2-13/</t>
+        </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-90-m%c2%b2-au-rez-de-chausseearcade-of-approx-90-m%c2%b2-on-first-floor-rive-geneve-centre-1270-1271-2-13/</t>
+          <t>2026-03-26 10:04:42</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2026-03-26 10:04:42</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2026-03-17 21:42:39</t>
+          <t>2026-04-24 21:53:00</t>
         </is>
       </c>
     </row>
@@ -1545,48 +1409,46 @@
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="n">
+      <c r="C20" t="n">
         <v>80</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Plainpalais</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>50</v>
+      </c>
       <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>50</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-80m%c2%b2-avec-depot-denv-30m%c2%b2-au-sous-solarcade-of-approx-80m%c2%b2-with-storage-area-of-approx-30m%c2%b2-in-the-base-plainpalais-820-821-1-17/</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denv-80m%c2%b2-avec-depot-denv-30m%c2%b2-au-sous-solarcade-of-approx-80m%c2%b2-with-storage-area-of-approx-30m%c2%b2-in-the-base-plainpalais-820-821-1-17/</t>
+          <t>2026-03-26 10:04:42</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2026-03-26 10:04:42</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2026-03-17 21:42:39</t>
+          <t>2026-04-24 21:53:00</t>
         </is>
       </c>
     </row>
@@ -1597,48 +1459,46 @@
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="n">
+      <c r="C21" t="n">
         <v>82</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Plainpalais</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>50</v>
+      </c>
       <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>50</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denviron-82-m%c2%b2-au-rez-de-chaussee82-m%c2%b2-arcade-on-ground-floor-plainpalais-9680-9681-1-13/</t>
+        </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>2026-03-16 23:21:26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.rosset.ch/louer/locaux-commerciaux/arcade-commerce/arcade-denviron-82-m%c2%b2-au-rez-de-chaussee82-m%c2%b2-arcade-on-ground-floor-plainpalais-9680-9681-1-13/</t>
+          <t>2026-03-26 10:04:42</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-03-16 23:21:26</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2026-03-26 10:04:42</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2026-03-17 21:42:39</t>
+          <t>2026-04-24 21:53:00</t>
         </is>
       </c>
     </row>
@@ -1653,46 +1513,44 @@
           <t>ACACIAS - CHF 374.-/m2 - Arcade d'environ 72m² Jonction-Plainpalais-Arve Rive, Les Acacias Loyer CHF 2’245.-</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="n">
+      <c r="C22" t="n">
         <v>72</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Rive</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>50</v>
+      </c>
       <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>50</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://www.pilet-renaud.ch/fr/a-louer//acacias-chf-374-m2-arcade-denviron-72m--8598</t>
+        </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.pilet-renaud.ch/fr/a-louer//acacias-chf-374-m2-arcade-denviron-72m--8598</t>
+          <t>2026-03-19 07:04:36</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
-        <is>
-          <t>2026-03-16 23:49:00</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2026-03-19 07:04:36</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
         <is>
           <t>2026-03-19 09:52:14</t>
         </is>
@@ -1709,46 +1567,40 @@
           <t xml:space="preserve">il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade </t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="n">
+      <c r="C23" t="n">
         <v>260</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>il y a 2 mois Naef Immobilier – Location 260 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 260m2 à louer  Quartier des Charmilles, Genève 260 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 12’014 CHF 554 m² / year</t>
-        </is>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>50</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>50</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-95R9-G6P5</t>
+        </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-95R9-G6P5</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -1765,50 +1617,44 @@
           <t xml:space="preserve">il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système </t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="n">
+      <c r="C24" t="n">
         <v>164</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Rive</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 164 m² • Bureau Cours De Rive 11, 1204 Genève Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande - Naef Immobilier – Location Bureau à louer Cours De Rive 11, 1204 Genève Bureaux de standing d'env 164 m² 164 m² • Bureau Système de climatisation Internet fibre optique Spacieuse entrée Prix sur demande</t>
-        </is>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>45</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="n">
-        <v>45</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/11-cours-de-rive-1204-geneve-VBG4-7VZQ</t>
+        </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/11-cours-de-rive-1204-geneve-VBG4-7VZQ</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -1825,46 +1671,40 @@
           <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade c</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="n">
+      <c r="C25" t="n">
         <v>130</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>il y a 2 mois Naef Immobilier – Location 130 m² • Arcade Rue Des Charmilles 3, 1203 Genève Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year Naef Immobilier – Location Arcade à louer Rue Des Charmilles 3, 1203 Genève Arcade commerciale env 130m2 à louer  Quartier des Charmilles, Genève 130 m² • Arcade Espace ouvert, aménagement flexible Belle visibilité sur rue Accès facile aux transports publics CHF 6’007 CHF 554 m² / year</t>
-        </is>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>40</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>40</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-XEG4-9ONV</t>
+        </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/3-rue-des-charmilles-1203-geneve-XEG4-9ONV</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -1881,46 +1721,44 @@
           <t>Estimer</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="n">
+      <c r="C26" t="n">
         <v>59</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Champel</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>35</v>
+      </c>
       <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>35</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://www.pilet-renaud.ch/fr/accueil/estimer</t>
+        </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.pilet-renaud.ch/fr/accueil/estimer</t>
+          <t>2026-03-26 07:16:04</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
-        <is>
-          <t>2026-03-16 23:49:00</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2026-03-26 07:16:04</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
         <is>
           <t>2026-03-26 08:41:35</t>
         </is>
@@ -1937,46 +1775,44 @@
           <t>Contact</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="n">
+      <c r="C27" t="n">
         <v>59</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Champel</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>35</v>
+      </c>
       <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>35</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://www.pilet-renaud.ch/fr/accueil/contact</t>
+        </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-16 23:49:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.pilet-renaud.ch/fr/accueil/contact</t>
+          <t>2026-03-26 07:16:04</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
-        <is>
-          <t>2026-03-16 23:49:00</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2026-03-26 07:16:04</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
         <is>
           <t>2026-03-26 08:41:35</t>
         </is>
@@ -1993,46 +1829,40 @@
           <t xml:space="preserve">il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • </t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
+      <c r="C28" t="n">
         <v>770</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>il y a 1 mois Zimmermann Immobilier 770 m² • Bureau Rue Jean- Jaquet, 1201 Genève Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year Zimmermann Immobilier Bureau à louer Rue Jean- Jaquet, 1201 Genève Bureaux aux Pâquis 770 m² • Bureau Superbe terrasse sur le toit Salle de conférence spacieuse Emplacement privilégié près du lac CHF 23’000 CHF 358 m² / year</t>
-        </is>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>35</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="n">
-        <v>35</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/rue-jean-jaquet-1201-geneve-WRG4-9WBO</t>
+        </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/rue-jean-jaquet-1201-geneve-WRG4-9WBO</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2049,46 +1879,40 @@
           <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Sur</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="n">
+      <c r="C29" t="n">
         <v>1351</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 1351 m² • Bureau Rue Barton 7, 1201 Genève Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande - Naef Immobilier – Location Bureau à louer Rue Barton 7, 1201 Genève Hypercentre - Surface de 1'351 m² sur deux niveaux 1351 m² • Bureau Emplacement privilégié près du lac Surface spacieuse de 1'351 m² Architecture unique avec hauteurs sous plafond Prix sur demande</t>
-        </is>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>35</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="n">
-        <v>35</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/7-rue-barton-1201-geneve-MXG4-NW29</t>
+        </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/7-rue-barton-1201-geneve-MXG4-NW29</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2105,46 +1929,40 @@
           <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genèv</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="n">
+      <c r="C30" t="n">
         <v>205</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>il y a 4 mois Naef Immobilier – Location 205 m² • Bureau Rue De Lausanne 82, 1202 Genève Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year Naef Immobilier – Location Bureau à louer Rue De Lausanne 82, 1202 Genève Rue de Lausanne - Bureaux d'env. 205 m² 205 m² • Bureau Emplacement stratégique près de l'ONU Espace rénové et personnalisable Places de parking et dépôts disponibles CHF 9’139 CHF 535 m² / year</t>
-        </is>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>35</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="n">
-        <v>35</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-WRG4-DVXX</t>
+        </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/82-rue-de-lausanne-1202-geneve-WRG4-DVXX</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2162,47 +1980,39 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>550</v>
-      </c>
-      <c r="D31" t="n">
         <v>22</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>il y a 28 jours Zimmermann Immobilier 2 pièces • 22 m² • Bureau Place De Cornavin, 1201 Genève Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year Zimmermann Immobilier Bureau à louer Place De Cornavin, 1201 Genève Bureau privatif de 14 m² dans grand espace partagé- 14 m² - en face de la Gare Cornavin 2 pièces • 22 m² • Bureau Emplacement idéal près de la gare Design lumineux et spacieux Accès aux commodités partagées CHF 1’550 CHF 845 m² / year</t>
-        </is>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>30</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/place-de-cornavin-1201-geneve-VBG4-9ZEO</t>
+        </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/place-de-cornavin-1201-geneve-VBG4-9ZEO</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2220,47 +2030,41 @@
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Plainpalais</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>il y a 1 mois Naef Immobilier – Location Bureau Rue Des Deux-Ponts 27, 1205 Genève Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178 - Naef Immobilier – Location Bureau à louer Rue Des Deux-Ponts 27, 1205 Genève Emplacement publicitaire pour une enseigne - Genève Plainpalais Bureau Excellente visibilité Situé dans un secteur animé Position au 7ème étage CHF 1’178</t>
-        </is>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>20</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="n">
-        <v>20</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/27-rue-des-deux-ponts-1205-geneve-23ZJ-9XPW</t>
+        </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/27-rue-des-deux-ponts-1205-geneve-23ZJ-9XPW</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2278,47 +2082,41 @@
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Eaux-Vives</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Eaux-Vives - Lac</t>
-        </is>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>20</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="n">
-        <v>20</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-eaux-vives-lac/commercial</t>
+        </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-eaux-vives-lac/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2336,47 +2134,41 @@
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Plainpalais</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Jonction - Plainpalais</t>
-        </is>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>20</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="n">
-        <v>20</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-jonction-plainpalais/commercial</t>
+        </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-jonction-plainpalais/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2394,47 +2186,41 @@
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Champel</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Champel - Roseraie</t>
-        </is>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>20</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="n">
-        <v>20</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-champel-roseraie/commercial</t>
+        </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-champel-roseraie/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2452,47 +2238,41 @@
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Eaux-Vives</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>il y a 2 mois NSR-Group S.A Garage Chemin de Roches, 1207 Genève Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400 - NSR-Group S.A Garage à louer Chemin de Roches, 1207 Genève Eaux-Vives - Box zu vermieten Garage Emplacement facilement accessible Portail de sécurité manuel Disponibilité immédiate CHF 400</t>
-        </is>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>20</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="n">
-        <v>20</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/chemin-de-roches-1207-geneve-8VBP-BWZW</t>
+        </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/chemin-de-roches-1207-geneve-8VBP-BWZW</t>
+          <t>2026-03-16 10:10:13</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>2026-03-16 10:10:13</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
         <is>
           <t>2026-03-16 13:22:39</t>
         </is>
@@ -2509,46 +2289,40 @@
           <t>il y a 3 jours Segimo SA Bureau 1203 Genève 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000 - Segimo SA Bureau à louer 1203 Genève Coworking professionnel pour architecte dans les locaux d'un promoteur immobilier à 1203 Genève Bureau 35 m² entièrement rénovés Cui</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="n">
+      <c r="C37" t="n">
         <v>35</v>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>il y a 3 jours Segimo SA Bureau 1203 Genève 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000 - Segimo SA Bureau à louer 1203 Genève Coworking professionnel pour architecte dans les locaux d'un promoteur immobilier à 1203 Genève Bureau 35 m² entièrement rénovés Cuisine et WC partagés Mobilier de bureau inclus CHF 1’000</t>
-        </is>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="n">
-        <v>10</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-KQNL-GWW5</t>
+        </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-16 16:10:21</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-KQNL-GWW5</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
-        <is>
-          <t>2026-03-16 16:10:21</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2565,46 +2339,40 @@
           <t>il y a 4 heures Segimo SA 35 m² • Bureau 1203 Genève Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande - Segimo SA Bureau à louer 1203 Genève 35 m² • Bureau Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="n">
+      <c r="C38" t="n">
         <v>35</v>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>il y a 4 heures Segimo SA 35 m² • Bureau 1203 Genève Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande - Segimo SA Bureau à louer 1203 Genève 35 m² • Bureau Intérieurs entièrement rénovés Cuisine et WC partagés Wi-Fi et ménage inclus Prix sur demande</t>
-        </is>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="n">
-        <v>10</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-8OOA-XD6Z</t>
+        </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-8OOA-XD6Z</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2621,46 +2389,40 @@
           <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="n">
+      <c r="C39" t="n">
         <v>35</v>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>il y a 3 jours Segimo SA 35 m² • Commercial 1203 Genève Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year Segimo SA Commercial à louer 1203 Genève 35m2 pour architecte 35 m² • Commercial Cuisine à partager WC à partager Ménage compris CHF 1’000 CHF 343 m² / year</t>
-        </is>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="n">
-        <v>10</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-Y235-5V7W</t>
+        </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial/1203-geneve-Y235-5V7W</t>
+          <t>2026-03-16 13:22:39</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-03-16 13:22:39</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
         <is>
           <t>2026-03-16 16:10:21</t>
         </is>
@@ -2679,42 +2441,36 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Local commercial</t>
-        </is>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/commercial</t>
+        </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2733,42 +2489,36 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Canton de Genève</t>
-        </is>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/canton-geneve/commercial</t>
+        </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/canton-geneve/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2787,42 +2537,36 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer</t>
-        </is>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/ville-geneve/commercial</t>
+        </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-geneve/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2841,42 +2585,36 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Bouchet - Moillebeau</t>
-        </is>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-bouchet-moillebeau/commercial</t>
+        </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-bouchet-moillebeau/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2895,42 +2633,36 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Cluse - Philosophes</t>
-        </is>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-cluse-philosophes/commercial</t>
+        </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-cluse-philosophes/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -2949,42 +2681,36 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Grand-Pré - Vermont</t>
-        </is>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-grand-pre-vermont/commercial</t>
+        </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-grand-pre-vermont/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3003,42 +2729,36 @@
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à St-Gervais - Chantepoulet</t>
-        </is>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-st-gervais-chantepoulet/commercial</t>
+        </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-st-gervais-chantepoulet/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3057,42 +2777,36 @@
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Pâquis - Navigation</t>
-        </is>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-paquis-navigation/commercial</t>
+        </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-paquis-navigation/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3111,42 +2825,36 @@
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à ONU - Rigot</t>
-        </is>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-onu-rigot/commercial</t>
+        </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-onu-rigot/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3165,42 +2873,36 @@
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Sécheron - Prieuré</t>
-        </is>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-secheron-prieure/commercial</t>
+        </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-secheron-prieure/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3219,42 +2921,36 @@
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Cité - Centre</t>
-        </is>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-cite-centre/commercial</t>
+        </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-cite-centre/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3273,42 +2969,36 @@
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Charmilles - Châtelaine</t>
-        </is>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-charmilles-chatelaine/commercial</t>
+        </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-charmilles-chatelaine/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3327,42 +3017,36 @@
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à St-Jean - Aire</t>
-        </is>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-st-jean-aire/commercial</t>
+        </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-st-jean-aire/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3381,42 +3065,36 @@
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Florissant - Malagnou</t>
-        </is>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-florissant-malagnou/commercial</t>
+        </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-florissant-malagnou/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3434,47 +3112,41 @@
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Acacias</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Bâtie - Acacias</t>
-        </is>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-batie-acacias/commercial</t>
+        </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-batie-acacias/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3493,42 +3165,36 @@
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Délices - Grottes</t>
-        </is>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/quartier-delices-grottes/commercial</t>
+        </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/quartier-delices-grottes/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3546,47 +3212,41 @@
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Acacias</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Les Acacias (1227)</t>
-        </is>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1227-les-acacias/commercial</t>
+        </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1227-les-acacias/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3605,42 +3265,36 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Vernier</t>
-        </is>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/ville-vernier/commercial</t>
+        </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-vernier/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3659,42 +3313,36 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Lancy</t>
-        </is>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/ville-lancy/commercial</t>
+        </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-lancy/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3713,42 +3361,36 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Meyrin</t>
-        </is>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/ville-meyrin/commercial</t>
+        </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-meyrin/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3766,47 +3408,41 @@
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Carouge</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Carouge GE (1227)</t>
-        </is>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1227-carouge-ge/commercial</t>
+        </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1227-carouge-ge/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3825,42 +3461,36 @@
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Onex (1213)</t>
-        </is>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1213-onex/commercial</t>
+        </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1213-onex/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3879,42 +3509,36 @@
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Thônex (1226)</t>
-        </is>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1226-thonex/commercial</t>
+        </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1226-thonex/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3933,42 +3557,36 @@
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Le Grand-Saconnex</t>
-        </is>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/ville-le-grand-saconnex/commercial</t>
+        </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-le-grand-saconnex/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -3987,42 +3605,36 @@
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Chêne-Bougeries</t>
-        </is>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/ville-chene-bougeries/commercial</t>
+        </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-chene-bougeries/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -4041,42 +3653,36 @@
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Veyrier</t>
-        </is>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/ville-veyrier/commercial</t>
+        </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/ville-veyrier/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -4095,42 +3701,36 @@
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Plan-les-Ouates (1228)</t>
-        </is>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1228-plan-les-ouates/commercial</t>
+        </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1228-plan-les-ouates/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -4149,42 +3749,36 @@
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Bernex (1233)</t>
-        </is>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1233-bernex/commercial</t>
+        </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1233-bernex/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -4203,42 +3797,36 @@
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Locaux commerciaux à louer à Chêne-Bourg (1225)</t>
-        </is>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://realadvisor.ch/fr/louer/1225-chene-bourg/commercial</t>
+        </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-15 23:33:16</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://realadvisor.ch/fr/louer/1225-chene-bourg/commercial</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
-        <is>
-          <t>2026-03-15 23:33:16</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
@@ -4257,42 +3845,36 @@
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>+41 21 313 43 13 F. +41 21 313 43 10</t>
-        </is>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>tel: +41 21 313 43 10</t>
+        </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>2026-03-16 02:45:59</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>tel: +41 21 313 43 10</t>
+          <t>2026-03-16 19:09:59</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
-        <is>
-          <t>2026-03-16 02:45:59</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>2026-03-16 19:09:59</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
         <is>
           <t>2026-03-16 20:00:43</t>
         </is>
